--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Текущая книга График" sheetId="5" r:id="rId3"/>
     <sheet name="Одежда" sheetId="3" r:id="rId4"/>
     <sheet name="Спорт" sheetId="4" r:id="rId5"/>
+    <sheet name="Шульте" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Кино!$A$1:$I$221</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="417">
   <si>
     <t>№</t>
   </si>
@@ -1293,6 +1294,12 @@
   </si>
   <si>
     <t>К востоку от Эдема</t>
+  </si>
+  <si>
+    <t>5х5</t>
+  </si>
+  <si>
+    <t>6х6</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1312,7 @@
     <numFmt numFmtId="166" formatCode="mmm\.yy"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1364,8 +1371,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Antique Olive Compact"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1414,8 +1428,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1479,11 +1499,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1620,6 +1655,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9203,4 +9253,216 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="8"/>
+    <col min="2" max="2" width="10.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="55" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>415</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="54">
+        <v>1</v>
+      </c>
+      <c r="B2" s="57">
+        <v>46289</v>
+      </c>
+      <c r="C2" s="58">
+        <v>3.9583333333333331E-2</v>
+      </c>
+      <c r="D2" s="58">
+        <v>8.4722222222222213E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -14,13 +14,12 @@
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
     <sheet name="Книги" sheetId="2" r:id="rId2"/>
-    <sheet name="Текущая книга График" sheetId="5" r:id="rId3"/>
-    <sheet name="Одежда" sheetId="3" r:id="rId4"/>
-    <sheet name="Спорт" sheetId="4" r:id="rId5"/>
-    <sheet name="Шульте" sheetId="6" r:id="rId6"/>
+    <sheet name="Одежда" sheetId="3" r:id="rId3"/>
+    <sheet name="Спорт" sheetId="4" r:id="rId4"/>
+    <sheet name="Шульте" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Кино!$A$1:$I$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Кино!$A$1:$J$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Книги!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="432">
   <si>
     <t>№</t>
   </si>
@@ -1274,12 +1273,6 @@
 80 кг - 2 по 10</t>
   </si>
   <si>
-    <t>Число</t>
-  </si>
-  <si>
-    <t>Страница</t>
-  </si>
-  <si>
     <t>Джек Лондон</t>
   </si>
   <si>
@@ -1320,6 +1313,42 @@
   </si>
   <si>
     <t>Реквием по мечте</t>
+  </si>
+  <si>
+    <t>Мишель Гондри</t>
+  </si>
+  <si>
+    <t>Вечное сияние чистого разума</t>
+  </si>
+  <si>
+    <t>Майкл Бэй</t>
+  </si>
+  <si>
+    <t>Перл-Харбор</t>
+  </si>
+  <si>
+    <t>Пролетая над гнездом кукушки</t>
+  </si>
+  <si>
+    <t>Милош Форман</t>
+  </si>
+  <si>
+    <t>Очень смешно позитивно и тепло</t>
+  </si>
+  <si>
+    <t>Теория игр</t>
+  </si>
+  <si>
+    <t>Атомные привычки</t>
+  </si>
+  <si>
+    <t>Хаим Шапира</t>
+  </si>
+  <si>
+    <t>Джеймс Клир</t>
+  </si>
+  <si>
+    <t>Оценка Ани</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1420,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1425,12 +1454,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1524,7 +1547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1623,10 +1646,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1642,7 +1661,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1986,21 +2005,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I242"/>
+  <dimension ref="A1:J242"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="8"/>
     <col min="2" max="2" width="24.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="8" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="43.28515625" style="8" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" style="8" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" style="8" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="8"/>
+    <col min="7" max="9" width="14.85546875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" style="8" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2026,10 +2045,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1">
+    <row r="2" spans="1:10" ht="30" customHeight="1">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -2054,11 +2076,14 @@
       <c r="H2" s="10">
         <v>8</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="10">
+        <v>7</v>
+      </c>
+      <c r="J2" s="14">
         <v>46184</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1">
+    <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -2079,9 +2104,10 @@
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="10"/>
-      <c r="I3" s="13"/>
-    </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1">
+      <c r="I3" s="10"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -2106,11 +2132,12 @@
       <c r="H4" s="10">
         <v>7</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="10"/>
+      <c r="J4" s="14">
         <v>46187</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1">
+    <row r="5" spans="1:10" ht="30" customHeight="1">
       <c r="A5" s="10">
         <v>4</v>
       </c>
@@ -2131,9 +2158,10 @@
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="10"/>
-      <c r="I5" s="13"/>
-    </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1">
+      <c r="I5" s="10"/>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -2154,9 +2182,10 @@
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="13"/>
-    </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1">
+      <c r="I6" s="10"/>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1">
       <c r="A7" s="10">
         <v>6</v>
       </c>
@@ -2177,9 +2206,10 @@
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="10"/>
-      <c r="I7" s="13"/>
-    </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1">
+      <c r="I7" s="10"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -2200,9 +2230,10 @@
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="10"/>
-      <c r="I8" s="13"/>
-    </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1">
+      <c r="I8" s="10"/>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1">
       <c r="A9" s="10">
         <v>8</v>
       </c>
@@ -2223,9 +2254,10 @@
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="10"/>
-      <c r="I9" s="13"/>
-    </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1">
+      <c r="I9" s="10"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:10" ht="30" customHeight="1">
       <c r="A10" s="10">
         <v>9</v>
       </c>
@@ -2246,9 +2278,10 @@
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="10"/>
-      <c r="I10" s="13"/>
-    </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1">
+      <c r="I10" s="10"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="1:10" ht="30" customHeight="1">
       <c r="A11" s="10">
         <v>10</v>
       </c>
@@ -2269,9 +2302,10 @@
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="10"/>
-      <c r="I11" s="13"/>
-    </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1">
+      <c r="I11" s="10"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -2292,9 +2326,10 @@
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="10"/>
-      <c r="I12" s="13"/>
-    </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1">
+      <c r="I12" s="10"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1">
       <c r="A13" s="10">
         <v>12</v>
       </c>
@@ -2315,9 +2350,10 @@
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="10"/>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1">
+      <c r="I13" s="10"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="1:10" ht="30" customHeight="1">
       <c r="A14" s="10">
         <v>13</v>
       </c>
@@ -2338,9 +2374,10 @@
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="10"/>
-      <c r="I14" s="13"/>
-    </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1">
+      <c r="I14" s="10"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1">
       <c r="A15" s="10">
         <v>14</v>
       </c>
@@ -2361,9 +2398,10 @@
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="10"/>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1">
+      <c r="I15" s="10"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" ht="30" customHeight="1">
       <c r="A16" s="10">
         <v>15</v>
       </c>
@@ -2384,9 +2422,10 @@
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="10"/>
-      <c r="I16" s="13"/>
-    </row>
-    <row r="17" spans="1:9" ht="30" customHeight="1">
+      <c r="I16" s="10"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" customHeight="1">
       <c r="A17" s="10">
         <v>16</v>
       </c>
@@ -2407,9 +2446,10 @@
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="10"/>
-      <c r="I17" s="13"/>
-    </row>
-    <row r="18" spans="1:9" ht="30" customHeight="1">
+      <c r="I17" s="10"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -2434,11 +2474,12 @@
       <c r="H18" s="10">
         <v>9</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="10"/>
+      <c r="J18" s="15">
         <v>45931</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30" customHeight="1">
+    <row r="19" spans="1:10" ht="30" customHeight="1">
       <c r="A19" s="10">
         <v>18</v>
       </c>
@@ -2459,9 +2500,10 @@
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="10"/>
-      <c r="I19" s="13"/>
-    </row>
-    <row r="20" spans="1:9" ht="30" customHeight="1">
+      <c r="I19" s="10"/>
+      <c r="J19" s="13"/>
+    </row>
+    <row r="20" spans="1:10" ht="30" customHeight="1">
       <c r="A20" s="10">
         <v>19</v>
       </c>
@@ -2482,9 +2524,10 @@
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="10"/>
-      <c r="I20" s="13"/>
-    </row>
-    <row r="21" spans="1:9" ht="30" customHeight="1">
+      <c r="I20" s="10"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="1:10" ht="30" customHeight="1">
       <c r="A21" s="10">
         <v>20</v>
       </c>
@@ -2505,9 +2548,10 @@
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="10"/>
-      <c r="I21" s="13"/>
-    </row>
-    <row r="22" spans="1:9" ht="30" customHeight="1">
+      <c r="I21" s="10"/>
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" spans="1:10" ht="30" customHeight="1">
       <c r="A22" s="10">
         <v>21</v>
       </c>
@@ -2532,11 +2576,12 @@
       <c r="H22" s="10">
         <v>7</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="10"/>
+      <c r="J22" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30" customHeight="1">
+    <row r="23" spans="1:10" ht="30" customHeight="1">
       <c r="A23" s="10">
         <v>22</v>
       </c>
@@ -2561,11 +2606,12 @@
       <c r="H23" s="10">
         <v>6</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="10"/>
+      <c r="J23" s="15">
         <v>45870</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30" customHeight="1">
+    <row r="24" spans="1:10" ht="30" customHeight="1">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -2586,9 +2632,10 @@
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="10"/>
-      <c r="I24" s="13"/>
-    </row>
-    <row r="25" spans="1:9" ht="30" customHeight="1">
+      <c r="I24" s="10"/>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1">
       <c r="A25" s="10">
         <v>24</v>
       </c>
@@ -2609,9 +2656,10 @@
       </c>
       <c r="G25" s="11"/>
       <c r="H25" s="10"/>
-      <c r="I25" s="13"/>
-    </row>
-    <row r="26" spans="1:9" ht="30" customHeight="1">
+      <c r="I25" s="10"/>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1">
       <c r="A26" s="10">
         <v>25</v>
       </c>
@@ -2636,11 +2684,12 @@
       <c r="H26" s="10">
         <v>9</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="10"/>
+      <c r="J26" s="15">
         <v>45809</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30" customHeight="1">
+    <row r="27" spans="1:10" ht="30" customHeight="1">
       <c r="A27" s="10">
         <v>26</v>
       </c>
@@ -2665,11 +2714,12 @@
       <c r="H27" s="10">
         <v>8</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="10"/>
+      <c r="J27" s="15">
         <v>45809</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="30" customHeight="1">
+    <row r="28" spans="1:10" ht="30" customHeight="1">
       <c r="A28" s="10">
         <v>27</v>
       </c>
@@ -2694,11 +2744,12 @@
       <c r="H28" s="10">
         <v>6</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="10"/>
+      <c r="J28" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="30" customHeight="1">
+    <row r="29" spans="1:10" ht="30" customHeight="1">
       <c r="A29" s="10">
         <v>28</v>
       </c>
@@ -2723,11 +2774,12 @@
       <c r="H29" s="10">
         <v>7</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="10"/>
+      <c r="J29" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="30" customHeight="1">
+    <row r="30" spans="1:10" ht="30" customHeight="1">
       <c r="A30" s="10">
         <v>29</v>
       </c>
@@ -2752,11 +2804,12 @@
       <c r="H30" s="10">
         <v>8</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="10"/>
+      <c r="J30" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="30" customHeight="1">
+    <row r="31" spans="1:10" ht="30" customHeight="1">
       <c r="A31" s="10">
         <v>30</v>
       </c>
@@ -2781,11 +2834,12 @@
       <c r="H31" s="10">
         <v>8</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="10"/>
+      <c r="J31" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="30" customHeight="1">
+    <row r="32" spans="1:10" ht="30" customHeight="1">
       <c r="A32" s="10">
         <v>31</v>
       </c>
@@ -2810,11 +2864,12 @@
       <c r="H32" s="10">
         <v>8</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="10"/>
+      <c r="J32" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="30" customHeight="1">
+    <row r="33" spans="1:10" ht="30" customHeight="1">
       <c r="A33" s="10">
         <v>32</v>
       </c>
@@ -2839,11 +2894,12 @@
       <c r="H33" s="10">
         <v>9</v>
       </c>
-      <c r="I33" s="13" t="s">
+      <c r="I33" s="10"/>
+      <c r="J33" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" customHeight="1">
+    <row r="34" spans="1:10" ht="30" customHeight="1">
       <c r="A34" s="10">
         <v>33</v>
       </c>
@@ -2868,11 +2924,12 @@
       <c r="H34" s="10">
         <v>9</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="I34" s="10"/>
+      <c r="J34" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="30" customHeight="1">
+    <row r="35" spans="1:10" ht="30" customHeight="1">
       <c r="A35" s="10">
         <v>34</v>
       </c>
@@ -2893,9 +2950,10 @@
       </c>
       <c r="G35" s="11"/>
       <c r="H35" s="10"/>
-      <c r="I35" s="13"/>
-    </row>
-    <row r="36" spans="1:9" ht="30" customHeight="1">
+      <c r="I35" s="10"/>
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="1:10" ht="30" customHeight="1">
       <c r="A36" s="10">
         <v>35</v>
       </c>
@@ -2920,11 +2978,12 @@
       <c r="H36" s="17">
         <v>8</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I36" s="17"/>
+      <c r="J36" s="15">
         <v>45717</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30" customHeight="1">
+    <row r="37" spans="1:10" ht="30" customHeight="1">
       <c r="A37" s="10">
         <v>36</v>
       </c>
@@ -2949,11 +3008,12 @@
       <c r="H37" s="17">
         <v>8</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I37" s="17"/>
+      <c r="J37" s="15">
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30" customHeight="1">
+    <row r="38" spans="1:10" ht="30" customHeight="1">
       <c r="A38" s="10">
         <v>37</v>
       </c>
@@ -2974,9 +3034,10 @@
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="18"/>
-      <c r="I38" s="13"/>
-    </row>
-    <row r="39" spans="1:9" ht="30" customHeight="1">
+      <c r="I38" s="18"/>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="1:10" ht="30" customHeight="1">
       <c r="A39" s="10">
         <v>38</v>
       </c>
@@ -2997,9 +3058,10 @@
       </c>
       <c r="G39" s="11"/>
       <c r="H39" s="18"/>
-      <c r="I39" s="13"/>
-    </row>
-    <row r="40" spans="1:9" ht="30" customHeight="1">
+      <c r="I39" s="18"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="1:10" ht="30" customHeight="1">
       <c r="A40" s="10">
         <v>39</v>
       </c>
@@ -3018,9 +3080,10 @@
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="18"/>
-      <c r="I40" s="13"/>
-    </row>
-    <row r="41" spans="1:9" ht="30" customHeight="1">
+      <c r="I40" s="18"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:10" ht="30" customHeight="1">
       <c r="A41" s="10">
         <v>40</v>
       </c>
@@ -3039,9 +3102,10 @@
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="18"/>
-      <c r="I41" s="13"/>
-    </row>
-    <row r="42" spans="1:9" ht="30" customHeight="1">
+      <c r="I41" s="18"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:10" ht="30" customHeight="1">
       <c r="A42" s="10">
         <v>41</v>
       </c>
@@ -3060,9 +3124,10 @@
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="18"/>
-      <c r="I42" s="13"/>
-    </row>
-    <row r="43" spans="1:9" ht="30" customHeight="1">
+      <c r="I42" s="18"/>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="1:10" ht="30" customHeight="1">
       <c r="A43" s="10">
         <v>42</v>
       </c>
@@ -3081,9 +3146,10 @@
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="18"/>
-      <c r="I43" s="13"/>
-    </row>
-    <row r="44" spans="1:9" ht="30" customHeight="1">
+      <c r="I43" s="18"/>
+      <c r="J43" s="13"/>
+    </row>
+    <row r="44" spans="1:10" ht="30" customHeight="1">
       <c r="A44" s="10">
         <v>43</v>
       </c>
@@ -3102,9 +3168,10 @@
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="18"/>
-      <c r="I44" s="13"/>
-    </row>
-    <row r="45" spans="1:9" ht="30" customHeight="1">
+      <c r="I44" s="18"/>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="1:10" ht="30" customHeight="1">
       <c r="A45" s="10">
         <v>44</v>
       </c>
@@ -3123,9 +3190,10 @@
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="18"/>
-      <c r="I45" s="13"/>
-    </row>
-    <row r="46" spans="1:9" ht="30" customHeight="1">
+      <c r="I45" s="18"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:10" ht="30" customHeight="1">
       <c r="A46" s="10">
         <v>45</v>
       </c>
@@ -3144,9 +3212,10 @@
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="18"/>
-      <c r="I46" s="13"/>
-    </row>
-    <row r="47" spans="1:9" ht="30" customHeight="1">
+      <c r="I46" s="18"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:10" ht="30" customHeight="1">
       <c r="A47" s="10">
         <v>46</v>
       </c>
@@ -3165,9 +3234,10 @@
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="18"/>
-      <c r="I47" s="13"/>
-    </row>
-    <row r="48" spans="1:9" ht="30" customHeight="1">
+      <c r="I47" s="18"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:10" ht="30" customHeight="1">
       <c r="A48" s="10">
         <v>47</v>
       </c>
@@ -3190,11 +3260,12 @@
       <c r="H48" s="17">
         <v>7</v>
       </c>
-      <c r="I48" s="15">
+      <c r="I48" s="17"/>
+      <c r="J48" s="15">
         <v>45931</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="30" customHeight="1">
+    <row r="49" spans="1:10" ht="30" customHeight="1">
       <c r="A49" s="10">
         <v>48</v>
       </c>
@@ -3213,9 +3284,10 @@
       </c>
       <c r="G49" s="11"/>
       <c r="H49" s="18"/>
-      <c r="I49" s="13"/>
-    </row>
-    <row r="50" spans="1:9" ht="30" customHeight="1">
+      <c r="I49" s="18"/>
+      <c r="J49" s="13"/>
+    </row>
+    <row r="50" spans="1:10" ht="30" customHeight="1">
       <c r="A50" s="10">
         <v>49</v>
       </c>
@@ -3234,9 +3306,10 @@
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="18"/>
-      <c r="I50" s="13"/>
-    </row>
-    <row r="51" spans="1:9" ht="30" customHeight="1">
+      <c r="I50" s="18"/>
+      <c r="J50" s="13"/>
+    </row>
+    <row r="51" spans="1:10" ht="30" customHeight="1">
       <c r="A51" s="10">
         <v>50</v>
       </c>
@@ -3255,9 +3328,10 @@
       </c>
       <c r="G51" s="11"/>
       <c r="H51" s="18"/>
-      <c r="I51" s="13"/>
-    </row>
-    <row r="52" spans="1:9" ht="30" customHeight="1">
+      <c r="I51" s="18"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:10" ht="30" customHeight="1">
       <c r="A52" s="10">
         <v>51</v>
       </c>
@@ -3280,11 +3354,12 @@
       <c r="H52" s="17">
         <v>8</v>
       </c>
-      <c r="I52" s="15">
+      <c r="I52" s="17"/>
+      <c r="J52" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="30" customHeight="1">
+    <row r="53" spans="1:10" ht="30" customHeight="1">
       <c r="A53" s="10">
         <v>52</v>
       </c>
@@ -3307,11 +3382,12 @@
       <c r="H53" s="17">
         <v>7</v>
       </c>
-      <c r="I53" s="15">
+      <c r="I53" s="17"/>
+      <c r="J53" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="30" customHeight="1">
+    <row r="54" spans="1:10" ht="30" customHeight="1">
       <c r="A54" s="10">
         <v>53</v>
       </c>
@@ -3334,11 +3410,12 @@
       <c r="H54" s="17">
         <v>5</v>
       </c>
-      <c r="I54" s="15">
+      <c r="I54" s="17"/>
+      <c r="J54" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="30" customHeight="1">
+    <row r="55" spans="1:10" ht="30" customHeight="1">
       <c r="A55" s="10">
         <v>54</v>
       </c>
@@ -3357,9 +3434,10 @@
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="18"/>
-      <c r="I55" s="13"/>
-    </row>
-    <row r="56" spans="1:9" ht="30" customHeight="1">
+      <c r="I55" s="18"/>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" spans="1:10" ht="30" customHeight="1">
       <c r="A56" s="10">
         <v>55</v>
       </c>
@@ -3378,9 +3456,10 @@
       </c>
       <c r="G56" s="11"/>
       <c r="H56" s="18"/>
-      <c r="I56" s="13"/>
-    </row>
-    <row r="57" spans="1:9" ht="30" customHeight="1">
+      <c r="I56" s="18"/>
+      <c r="J56" s="13"/>
+    </row>
+    <row r="57" spans="1:10" ht="30" customHeight="1">
       <c r="A57" s="10">
         <v>56</v>
       </c>
@@ -3399,9 +3478,10 @@
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="18"/>
-      <c r="I57" s="13"/>
-    </row>
-    <row r="58" spans="1:9" ht="30" customHeight="1">
+      <c r="I57" s="18"/>
+      <c r="J57" s="13"/>
+    </row>
+    <row r="58" spans="1:10" ht="30" customHeight="1">
       <c r="A58" s="10">
         <v>57</v>
       </c>
@@ -3424,11 +3504,12 @@
       <c r="H58" s="17">
         <v>7</v>
       </c>
-      <c r="I58" s="15">
+      <c r="I58" s="17"/>
+      <c r="J58" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="30" customHeight="1">
+    <row r="59" spans="1:10" ht="30" customHeight="1">
       <c r="A59" s="10">
         <v>58</v>
       </c>
@@ -3451,11 +3532,12 @@
       <c r="H59" s="17">
         <v>7</v>
       </c>
-      <c r="I59" s="15">
+      <c r="I59" s="17"/>
+      <c r="J59" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="30" customHeight="1">
+    <row r="60" spans="1:10" ht="30" customHeight="1">
       <c r="A60" s="10">
         <v>59</v>
       </c>
@@ -3478,11 +3560,12 @@
       <c r="H60" s="17">
         <v>8</v>
       </c>
-      <c r="I60" s="15">
+      <c r="I60" s="17"/>
+      <c r="J60" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="30" customHeight="1">
+    <row r="61" spans="1:10" ht="30" customHeight="1">
       <c r="A61" s="10">
         <v>60</v>
       </c>
@@ -3505,11 +3588,12 @@
       <c r="H61" s="17">
         <v>7</v>
       </c>
-      <c r="I61" s="15">
+      <c r="I61" s="17"/>
+      <c r="J61" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="30" customHeight="1">
+    <row r="62" spans="1:10" ht="30" customHeight="1">
       <c r="A62" s="10">
         <v>61</v>
       </c>
@@ -3528,9 +3612,10 @@
       </c>
       <c r="G62" s="11"/>
       <c r="H62" s="18"/>
-      <c r="I62" s="13"/>
-    </row>
-    <row r="63" spans="1:9" ht="30" customHeight="1">
+      <c r="I62" s="18"/>
+      <c r="J62" s="13"/>
+    </row>
+    <row r="63" spans="1:10" ht="30" customHeight="1">
       <c r="A63" s="10">
         <v>62</v>
       </c>
@@ -3553,11 +3638,12 @@
       <c r="H63" s="17">
         <v>8</v>
       </c>
-      <c r="I63" s="13">
+      <c r="I63" s="17"/>
+      <c r="J63" s="13">
         <v>2024</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="30" customHeight="1">
+    <row r="64" spans="1:10" ht="30" customHeight="1">
       <c r="A64" s="10">
         <v>63</v>
       </c>
@@ -3576,9 +3662,10 @@
       </c>
       <c r="G64" s="11"/>
       <c r="H64" s="18"/>
-      <c r="I64" s="13"/>
-    </row>
-    <row r="65" spans="1:9" ht="30" customHeight="1">
+      <c r="I64" s="18"/>
+      <c r="J64" s="13"/>
+    </row>
+    <row r="65" spans="1:10" ht="30" customHeight="1">
       <c r="A65" s="10">
         <v>64</v>
       </c>
@@ -3597,9 +3684,10 @@
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="18"/>
-      <c r="I65" s="13"/>
-    </row>
-    <row r="66" spans="1:9" ht="30" customHeight="1">
+      <c r="I65" s="18"/>
+      <c r="J65" s="13"/>
+    </row>
+    <row r="66" spans="1:10" ht="30" customHeight="1">
       <c r="A66" s="10">
         <v>65</v>
       </c>
@@ -3622,11 +3710,12 @@
       <c r="H66" s="17">
         <v>8</v>
       </c>
-      <c r="I66" s="13" t="s">
+      <c r="I66" s="17"/>
+      <c r="J66" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="30" customHeight="1">
+    <row r="67" spans="1:10" ht="30" customHeight="1">
       <c r="A67" s="10">
         <v>66</v>
       </c>
@@ -3649,11 +3738,12 @@
       <c r="H67" s="17">
         <v>8</v>
       </c>
-      <c r="I67" s="15">
+      <c r="I67" s="17"/>
+      <c r="J67" s="15">
         <v>46023</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="30" customHeight="1">
+    <row r="68" spans="1:10" ht="30" customHeight="1">
       <c r="A68" s="10">
         <v>67</v>
       </c>
@@ -3672,9 +3762,10 @@
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="18"/>
-      <c r="I68" s="13"/>
-    </row>
-    <row r="69" spans="1:9" ht="30" customHeight="1">
+      <c r="I68" s="18"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="1:10" ht="30" customHeight="1">
       <c r="A69" s="10">
         <v>68</v>
       </c>
@@ -3697,11 +3788,12 @@
       <c r="H69" s="17">
         <v>8</v>
       </c>
-      <c r="I69" s="13" t="s">
+      <c r="I69" s="17"/>
+      <c r="J69" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="30" customHeight="1">
+    <row r="70" spans="1:10" ht="30" customHeight="1">
       <c r="A70" s="10">
         <v>69</v>
       </c>
@@ -3720,9 +3812,10 @@
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="18"/>
-      <c r="I70" s="13"/>
-    </row>
-    <row r="71" spans="1:9" ht="30" customHeight="1">
+      <c r="I70" s="18"/>
+      <c r="J70" s="13"/>
+    </row>
+    <row r="71" spans="1:10" ht="30" customHeight="1">
       <c r="A71" s="10">
         <v>70</v>
       </c>
@@ -3745,11 +3838,12 @@
       <c r="H71" s="17">
         <v>8</v>
       </c>
-      <c r="I71" s="15">
+      <c r="I71" s="17"/>
+      <c r="J71" s="15">
         <v>46023</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="30" customHeight="1">
+    <row r="72" spans="1:10" ht="30" customHeight="1">
       <c r="A72" s="10">
         <v>71</v>
       </c>
@@ -3772,11 +3866,12 @@
       <c r="H72" s="17">
         <v>8</v>
       </c>
-      <c r="I72" s="13" t="s">
+      <c r="I72" s="17"/>
+      <c r="J72" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30" customHeight="1">
+    <row r="73" spans="1:10" ht="30" customHeight="1">
       <c r="A73" s="10">
         <v>72</v>
       </c>
@@ -3795,9 +3890,10 @@
       </c>
       <c r="G73" s="11"/>
       <c r="H73" s="18"/>
-      <c r="I73" s="13"/>
-    </row>
-    <row r="74" spans="1:9" ht="30" customHeight="1">
+      <c r="I73" s="18"/>
+      <c r="J73" s="13"/>
+    </row>
+    <row r="74" spans="1:10" ht="30" customHeight="1">
       <c r="A74" s="10">
         <v>73</v>
       </c>
@@ -3820,11 +3916,12 @@
       <c r="H74" s="17">
         <v>7</v>
       </c>
-      <c r="I74" s="15">
+      <c r="I74" s="17"/>
+      <c r="J74" s="15">
         <v>45962</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="30" customHeight="1">
+    <row r="75" spans="1:10" ht="30" customHeight="1">
       <c r="A75" s="10">
         <v>74</v>
       </c>
@@ -3847,11 +3944,12 @@
       <c r="H75" s="17">
         <v>6</v>
       </c>
-      <c r="I75" s="13" t="s">
+      <c r="I75" s="17"/>
+      <c r="J75" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="30" customHeight="1">
+    <row r="76" spans="1:10" ht="30" customHeight="1">
       <c r="A76" s="10">
         <v>75</v>
       </c>
@@ -3870,9 +3968,10 @@
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="18"/>
-      <c r="I76" s="13"/>
-    </row>
-    <row r="77" spans="1:9" ht="30" customHeight="1">
+      <c r="I76" s="18"/>
+      <c r="J76" s="13"/>
+    </row>
+    <row r="77" spans="1:10" ht="30" customHeight="1">
       <c r="A77" s="10">
         <v>76</v>
       </c>
@@ -3891,9 +3990,10 @@
       </c>
       <c r="G77" s="11"/>
       <c r="H77" s="18"/>
-      <c r="I77" s="13"/>
-    </row>
-    <row r="78" spans="1:9" ht="30" customHeight="1">
+      <c r="I77" s="18"/>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="1:10" ht="30" customHeight="1">
       <c r="A78" s="10">
         <v>77</v>
       </c>
@@ -3912,9 +4012,10 @@
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="18"/>
-      <c r="I78" s="13"/>
-    </row>
-    <row r="79" spans="1:9" ht="30" customHeight="1">
+      <c r="I78" s="18"/>
+      <c r="J78" s="13"/>
+    </row>
+    <row r="79" spans="1:10" ht="30" customHeight="1">
       <c r="A79" s="10">
         <v>78</v>
       </c>
@@ -3933,9 +4034,10 @@
       </c>
       <c r="G79" s="11"/>
       <c r="H79" s="18"/>
-      <c r="I79" s="13"/>
-    </row>
-    <row r="80" spans="1:9" ht="30" customHeight="1">
+      <c r="I79" s="18"/>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80" spans="1:10" ht="30" customHeight="1">
       <c r="A80" s="10">
         <v>79</v>
       </c>
@@ -3954,9 +4056,10 @@
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="18"/>
-      <c r="I80" s="13"/>
-    </row>
-    <row r="81" spans="1:9" ht="30" customHeight="1">
+      <c r="I80" s="18"/>
+      <c r="J80" s="13"/>
+    </row>
+    <row r="81" spans="1:10" ht="30" customHeight="1">
       <c r="A81" s="10">
         <v>80</v>
       </c>
@@ -3975,9 +4078,10 @@
       </c>
       <c r="G81" s="11"/>
       <c r="H81" s="18"/>
-      <c r="I81" s="13"/>
-    </row>
-    <row r="82" spans="1:9" ht="30" customHeight="1">
+      <c r="I81" s="18"/>
+      <c r="J81" s="13"/>
+    </row>
+    <row r="82" spans="1:10" ht="30" customHeight="1">
       <c r="A82" s="10">
         <v>81</v>
       </c>
@@ -3996,9 +4100,10 @@
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="18"/>
-      <c r="I82" s="13"/>
-    </row>
-    <row r="83" spans="1:9" ht="30" customHeight="1">
+      <c r="I82" s="18"/>
+      <c r="J82" s="13"/>
+    </row>
+    <row r="83" spans="1:10" ht="30" customHeight="1">
       <c r="A83" s="10">
         <v>82</v>
       </c>
@@ -4017,9 +4122,10 @@
       </c>
       <c r="G83" s="11"/>
       <c r="H83" s="18"/>
-      <c r="I83" s="13"/>
-    </row>
-    <row r="84" spans="1:9" ht="30" customHeight="1">
+      <c r="I83" s="18"/>
+      <c r="J83" s="13"/>
+    </row>
+    <row r="84" spans="1:10" ht="30" customHeight="1">
       <c r="A84" s="10">
         <v>83</v>
       </c>
@@ -4038,9 +4144,10 @@
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="18"/>
-      <c r="I84" s="13"/>
-    </row>
-    <row r="85" spans="1:9" ht="30" customHeight="1">
+      <c r="I84" s="18"/>
+      <c r="J84" s="13"/>
+    </row>
+    <row r="85" spans="1:10" ht="30" customHeight="1">
       <c r="A85" s="10">
         <v>84</v>
       </c>
@@ -4059,9 +4166,10 @@
       </c>
       <c r="G85" s="11"/>
       <c r="H85" s="18"/>
-      <c r="I85" s="13"/>
-    </row>
-    <row r="86" spans="1:9" ht="30" customHeight="1">
+      <c r="I85" s="18"/>
+      <c r="J85" s="13"/>
+    </row>
+    <row r="86" spans="1:10" ht="30" customHeight="1">
       <c r="A86" s="10">
         <v>85</v>
       </c>
@@ -4080,9 +4188,10 @@
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="18"/>
-      <c r="I86" s="13"/>
-    </row>
-    <row r="87" spans="1:9" ht="30" customHeight="1">
+      <c r="I86" s="18"/>
+      <c r="J86" s="13"/>
+    </row>
+    <row r="87" spans="1:10" ht="30" customHeight="1">
       <c r="A87" s="10">
         <v>86</v>
       </c>
@@ -4105,11 +4214,12 @@
       <c r="H87" s="17">
         <v>7</v>
       </c>
-      <c r="I87" s="13" t="s">
+      <c r="I87" s="17"/>
+      <c r="J87" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="30" customHeight="1">
+    <row r="88" spans="1:10" ht="30" customHeight="1">
       <c r="A88" s="10">
         <v>87</v>
       </c>
@@ -4128,9 +4238,10 @@
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="18"/>
-      <c r="I88" s="13"/>
-    </row>
-    <row r="89" spans="1:9" ht="30" customHeight="1">
+      <c r="I88" s="18"/>
+      <c r="J88" s="13"/>
+    </row>
+    <row r="89" spans="1:10" ht="30" customHeight="1">
       <c r="A89" s="10">
         <v>88</v>
       </c>
@@ -4149,9 +4260,10 @@
       </c>
       <c r="G89" s="11"/>
       <c r="H89" s="18"/>
-      <c r="I89" s="13"/>
-    </row>
-    <row r="90" spans="1:9" ht="30" customHeight="1">
+      <c r="I89" s="18"/>
+      <c r="J89" s="13"/>
+    </row>
+    <row r="90" spans="1:10" ht="30" customHeight="1">
       <c r="A90" s="10">
         <v>89</v>
       </c>
@@ -4170,9 +4282,10 @@
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="18"/>
-      <c r="I90" s="13"/>
-    </row>
-    <row r="91" spans="1:9" ht="30" customHeight="1">
+      <c r="I90" s="18"/>
+      <c r="J90" s="13"/>
+    </row>
+    <row r="91" spans="1:10" ht="30" customHeight="1">
       <c r="A91" s="10">
         <v>90</v>
       </c>
@@ -4191,9 +4304,10 @@
       </c>
       <c r="G91" s="11"/>
       <c r="H91" s="18"/>
-      <c r="I91" s="13"/>
-    </row>
-    <row r="92" spans="1:9" ht="30" customHeight="1">
+      <c r="I91" s="18"/>
+      <c r="J91" s="13"/>
+    </row>
+    <row r="92" spans="1:10" ht="30" customHeight="1">
       <c r="A92" s="10">
         <v>91</v>
       </c>
@@ -4212,9 +4326,10 @@
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="18"/>
-      <c r="I92" s="13"/>
-    </row>
-    <row r="93" spans="1:9" ht="30" customHeight="1">
+      <c r="I92" s="18"/>
+      <c r="J92" s="13"/>
+    </row>
+    <row r="93" spans="1:10" ht="30" customHeight="1">
       <c r="A93" s="10">
         <v>92</v>
       </c>
@@ -4233,9 +4348,10 @@
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="18"/>
-      <c r="I93" s="13"/>
-    </row>
-    <row r="94" spans="1:9" ht="30" customHeight="1">
+      <c r="I93" s="18"/>
+      <c r="J93" s="13"/>
+    </row>
+    <row r="94" spans="1:10" ht="30" customHeight="1">
       <c r="A94" s="10">
         <v>93</v>
       </c>
@@ -4258,11 +4374,12 @@
       <c r="H94" s="17">
         <v>7</v>
       </c>
-      <c r="I94" s="24" t="s">
+      <c r="I94" s="17"/>
+      <c r="J94" s="24" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="30" customHeight="1">
+    <row r="95" spans="1:10" ht="30" customHeight="1">
       <c r="A95" s="10">
         <v>94</v>
       </c>
@@ -4285,11 +4402,12 @@
       <c r="H95" s="17">
         <v>9</v>
       </c>
-      <c r="I95" s="15">
+      <c r="I95" s="17"/>
+      <c r="J95" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="30" customHeight="1">
+    <row r="96" spans="1:10" ht="30" customHeight="1">
       <c r="A96" s="10">
         <v>95</v>
       </c>
@@ -4308,9 +4426,10 @@
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="18"/>
-      <c r="I96" s="13"/>
-    </row>
-    <row r="97" spans="1:9" ht="30" customHeight="1">
+      <c r="I96" s="18"/>
+      <c r="J96" s="13"/>
+    </row>
+    <row r="97" spans="1:10" ht="30" customHeight="1">
       <c r="A97" s="10">
         <v>96</v>
       </c>
@@ -4329,9 +4448,10 @@
       </c>
       <c r="G97" s="11"/>
       <c r="H97" s="18"/>
-      <c r="I97" s="13"/>
-    </row>
-    <row r="98" spans="1:9" ht="30" customHeight="1">
+      <c r="I97" s="18"/>
+      <c r="J97" s="13"/>
+    </row>
+    <row r="98" spans="1:10" ht="30" customHeight="1">
       <c r="A98" s="10">
         <v>97</v>
       </c>
@@ -4350,9 +4470,10 @@
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="18"/>
-      <c r="I98" s="13"/>
-    </row>
-    <row r="99" spans="1:9" ht="30" customHeight="1">
+      <c r="I98" s="18"/>
+      <c r="J98" s="13"/>
+    </row>
+    <row r="99" spans="1:10" ht="30" customHeight="1">
       <c r="A99" s="10">
         <v>98</v>
       </c>
@@ -4371,9 +4492,10 @@
       </c>
       <c r="G99" s="11"/>
       <c r="H99" s="18"/>
-      <c r="I99" s="13"/>
-    </row>
-    <row r="100" spans="1:9" ht="30" customHeight="1">
+      <c r="I99" s="18"/>
+      <c r="J99" s="13"/>
+    </row>
+    <row r="100" spans="1:10" ht="30" customHeight="1">
       <c r="A100" s="10">
         <v>99</v>
       </c>
@@ -4392,9 +4514,10 @@
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="18"/>
-      <c r="I100" s="13"/>
-    </row>
-    <row r="101" spans="1:9" ht="30" customHeight="1">
+      <c r="I100" s="18"/>
+      <c r="J100" s="13"/>
+    </row>
+    <row r="101" spans="1:10" ht="30" customHeight="1">
       <c r="A101" s="10">
         <v>100</v>
       </c>
@@ -4413,9 +4536,10 @@
       </c>
       <c r="G101" s="11"/>
       <c r="H101" s="18"/>
-      <c r="I101" s="13"/>
-    </row>
-    <row r="102" spans="1:9" ht="30" customHeight="1">
+      <c r="I101" s="18"/>
+      <c r="J101" s="13"/>
+    </row>
+    <row r="102" spans="1:10" ht="30" customHeight="1">
       <c r="A102" s="10">
         <v>101</v>
       </c>
@@ -4434,9 +4558,10 @@
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="18"/>
-      <c r="I102" s="13"/>
-    </row>
-    <row r="103" spans="1:9" ht="30" customHeight="1">
+      <c r="I102" s="18"/>
+      <c r="J102" s="13"/>
+    </row>
+    <row r="103" spans="1:10" ht="30" customHeight="1">
       <c r="A103" s="10">
         <v>102</v>
       </c>
@@ -4459,11 +4584,12 @@
       <c r="H103" s="17">
         <v>6</v>
       </c>
-      <c r="I103" s="15">
+      <c r="I103" s="17"/>
+      <c r="J103" s="15">
         <v>46143</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="30" customHeight="1">
+    <row r="104" spans="1:10" ht="30" customHeight="1">
       <c r="A104" s="10">
         <v>103</v>
       </c>
@@ -4486,11 +4612,12 @@
       <c r="H104" s="17">
         <v>7</v>
       </c>
-      <c r="I104" s="13" t="s">
+      <c r="I104" s="17"/>
+      <c r="J104" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="30" customHeight="1">
+    <row r="105" spans="1:10" ht="30" customHeight="1">
       <c r="A105" s="10">
         <v>104</v>
       </c>
@@ -4513,11 +4640,12 @@
       <c r="H105" s="17">
         <v>8</v>
       </c>
-      <c r="I105" s="13" t="s">
+      <c r="I105" s="17"/>
+      <c r="J105" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="30" customHeight="1">
+    <row r="106" spans="1:10" ht="30" customHeight="1">
       <c r="A106" s="10">
         <v>105</v>
       </c>
@@ -4536,9 +4664,10 @@
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="18"/>
-      <c r="I106" s="13"/>
-    </row>
-    <row r="107" spans="1:9" ht="30" customHeight="1">
+      <c r="I106" s="18"/>
+      <c r="J106" s="13"/>
+    </row>
+    <row r="107" spans="1:10" ht="30" customHeight="1">
       <c r="A107" s="10">
         <v>106</v>
       </c>
@@ -4563,11 +4692,12 @@
       <c r="H107" s="17">
         <v>10</v>
       </c>
-      <c r="I107" s="15">
+      <c r="I107" s="17"/>
+      <c r="J107" s="15">
         <v>46082</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="30" customHeight="1">
+    <row r="108" spans="1:10" ht="30" customHeight="1">
       <c r="A108" s="10">
         <v>107</v>
       </c>
@@ -4590,11 +4720,12 @@
       <c r="H108" s="17">
         <v>8</v>
       </c>
-      <c r="I108" s="13" t="s">
+      <c r="I108" s="17"/>
+      <c r="J108" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="30" customHeight="1">
+    <row r="109" spans="1:10" ht="30" customHeight="1">
       <c r="A109" s="10">
         <v>108</v>
       </c>
@@ -4617,11 +4748,12 @@
       <c r="H109" s="17">
         <v>8</v>
       </c>
-      <c r="I109" s="15">
+      <c r="I109" s="17"/>
+      <c r="J109" s="15">
         <v>46082</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="30" customHeight="1">
+    <row r="110" spans="1:10" ht="30" customHeight="1">
       <c r="A110" s="10">
         <v>109</v>
       </c>
@@ -4644,11 +4776,12 @@
       <c r="H110" s="17">
         <v>8</v>
       </c>
-      <c r="I110" s="13" t="s">
+      <c r="I110" s="17"/>
+      <c r="J110" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="30" customHeight="1">
+    <row r="111" spans="1:10" ht="30" customHeight="1">
       <c r="A111" s="10">
         <v>110</v>
       </c>
@@ -4671,11 +4804,12 @@
       <c r="H111" s="17">
         <v>7</v>
       </c>
-      <c r="I111" s="15">
+      <c r="I111" s="17"/>
+      <c r="J111" s="15">
         <v>45231</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="30" customHeight="1">
+    <row r="112" spans="1:10" ht="30" customHeight="1">
       <c r="A112" s="10">
         <v>111</v>
       </c>
@@ -4695,14 +4829,15 @@
       <c r="G112" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H112" s="48">
+      <c r="H112" s="44">
         <v>7.7</v>
       </c>
-      <c r="I112" s="49">
+      <c r="I112" s="44"/>
+      <c r="J112" s="45">
         <v>46200</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="30" customHeight="1">
+    <row r="113" spans="1:10" ht="30" customHeight="1">
       <c r="A113" s="10">
         <v>112</v>
       </c>
@@ -4725,11 +4860,12 @@
       <c r="H113" s="10">
         <v>6</v>
       </c>
-      <c r="I113" s="15">
+      <c r="I113" s="10"/>
+      <c r="J113" s="15">
         <v>45717</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="30" customHeight="1">
+    <row r="114" spans="1:10" ht="30" customHeight="1">
       <c r="A114" s="10">
         <v>113</v>
       </c>
@@ -4752,11 +4888,12 @@
       <c r="H114" s="10">
         <v>7</v>
       </c>
-      <c r="I114" s="15">
+      <c r="I114" s="10"/>
+      <c r="J114" s="15">
         <v>45717</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="30" customHeight="1">
+    <row r="115" spans="1:10" ht="30" customHeight="1">
       <c r="A115" s="10">
         <v>114</v>
       </c>
@@ -4779,11 +4916,12 @@
       <c r="H115" s="10">
         <v>6</v>
       </c>
-      <c r="I115" s="15">
+      <c r="I115" s="10"/>
+      <c r="J115" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="30" customHeight="1">
+    <row r="116" spans="1:10" ht="30" customHeight="1">
       <c r="A116" s="10">
         <v>115</v>
       </c>
@@ -4806,11 +4944,12 @@
       <c r="H116" s="10">
         <v>6</v>
       </c>
-      <c r="I116" s="15">
+      <c r="I116" s="10"/>
+      <c r="J116" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="30" customHeight="1">
+    <row r="117" spans="1:10" ht="30" customHeight="1">
       <c r="A117" s="10">
         <v>116</v>
       </c>
@@ -4829,9 +4968,10 @@
       </c>
       <c r="G117" s="11"/>
       <c r="H117" s="10"/>
-      <c r="I117" s="13"/>
-    </row>
-    <row r="118" spans="1:9" ht="30" customHeight="1">
+      <c r="I117" s="10"/>
+      <c r="J117" s="13"/>
+    </row>
+    <row r="118" spans="1:10" ht="30" customHeight="1">
       <c r="A118" s="10">
         <v>117</v>
       </c>
@@ -4850,9 +4990,10 @@
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="10"/>
-      <c r="I118" s="13"/>
-    </row>
-    <row r="119" spans="1:9" ht="30" customHeight="1">
+      <c r="I118" s="10"/>
+      <c r="J118" s="13"/>
+    </row>
+    <row r="119" spans="1:10" ht="30" customHeight="1">
       <c r="A119" s="10">
         <v>118</v>
       </c>
@@ -4875,11 +5016,12 @@
       <c r="H119" s="10">
         <v>7</v>
       </c>
-      <c r="I119" s="13">
+      <c r="I119" s="10"/>
+      <c r="J119" s="13">
         <v>2023</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="30" customHeight="1">
+    <row r="120" spans="1:10" ht="30" customHeight="1">
       <c r="A120" s="10">
         <v>119</v>
       </c>
@@ -4904,11 +5046,12 @@
       <c r="H120" s="10">
         <v>8</v>
       </c>
-      <c r="I120" s="50">
+      <c r="I120" s="10"/>
+      <c r="J120" s="46">
         <v>46260</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="30" customHeight="1">
+    <row r="121" spans="1:10" ht="30" customHeight="1">
       <c r="A121" s="10">
         <v>120</v>
       </c>
@@ -4931,11 +5074,12 @@
       <c r="H121" s="10">
         <v>7</v>
       </c>
-      <c r="I121" s="13" t="s">
+      <c r="I121" s="10"/>
+      <c r="J121" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="30" customHeight="1">
+    <row r="122" spans="1:10" ht="30" customHeight="1">
       <c r="A122" s="10">
         <v>121</v>
       </c>
@@ -4958,11 +5102,12 @@
       <c r="H122" s="10">
         <v>7</v>
       </c>
-      <c r="I122" s="15">
+      <c r="I122" s="10"/>
+      <c r="J122" s="15">
         <v>44713</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="30" customHeight="1">
+    <row r="123" spans="1:10" ht="30" customHeight="1">
       <c r="A123" s="10">
         <v>122</v>
       </c>
@@ -4981,9 +5126,10 @@
       </c>
       <c r="G123" s="11"/>
       <c r="H123" s="10"/>
-      <c r="I123" s="13"/>
-    </row>
-    <row r="124" spans="1:9" ht="30" customHeight="1">
+      <c r="I123" s="10"/>
+      <c r="J123" s="13"/>
+    </row>
+    <row r="124" spans="1:10" ht="30" customHeight="1">
       <c r="A124" s="10">
         <v>123</v>
       </c>
@@ -5002,9 +5148,10 @@
       </c>
       <c r="G124" s="11"/>
       <c r="H124" s="10"/>
-      <c r="I124" s="13"/>
-    </row>
-    <row r="125" spans="1:9" ht="30" customHeight="1">
+      <c r="I124" s="10"/>
+      <c r="J124" s="13"/>
+    </row>
+    <row r="125" spans="1:10" ht="30" customHeight="1">
       <c r="A125" s="10">
         <v>124</v>
       </c>
@@ -5027,11 +5174,12 @@
       <c r="H125" s="10">
         <v>6</v>
       </c>
-      <c r="I125" s="14">
+      <c r="I125" s="10"/>
+      <c r="J125" s="14">
         <v>46171</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="30" customHeight="1">
+    <row r="126" spans="1:10" ht="30" customHeight="1">
       <c r="A126" s="10">
         <v>125</v>
       </c>
@@ -5056,11 +5204,12 @@
       <c r="H126" s="10">
         <v>9</v>
       </c>
-      <c r="I126" s="15">
+      <c r="I126" s="10"/>
+      <c r="J126" s="15">
         <v>45658</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="30" customHeight="1">
+    <row r="127" spans="1:10" ht="30" customHeight="1">
       <c r="A127" s="10">
         <v>126</v>
       </c>
@@ -5085,11 +5234,12 @@
       <c r="H127" s="10">
         <v>7</v>
       </c>
-      <c r="I127" s="15">
+      <c r="I127" s="10"/>
+      <c r="J127" s="15">
         <v>45748</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="30" customHeight="1">
+    <row r="128" spans="1:10" ht="30" customHeight="1">
       <c r="A128" s="10">
         <v>127</v>
       </c>
@@ -5114,11 +5264,12 @@
       <c r="H128" s="10">
         <v>6.5</v>
       </c>
-      <c r="I128" s="15">
+      <c r="I128" s="10"/>
+      <c r="J128" s="15">
         <v>45778</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="30" customHeight="1">
+    <row r="129" spans="1:10" ht="30" customHeight="1">
       <c r="A129" s="10">
         <v>128</v>
       </c>
@@ -5141,11 +5292,12 @@
       <c r="H129" s="10">
         <v>7</v>
       </c>
-      <c r="I129" s="15">
+      <c r="I129" s="10"/>
+      <c r="J129" s="15">
         <v>45778</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="30" customHeight="1">
+    <row r="130" spans="1:10" ht="30" customHeight="1">
       <c r="A130" s="10">
         <v>129</v>
       </c>
@@ -5168,11 +5320,12 @@
       <c r="H130" s="10">
         <v>7.5</v>
       </c>
-      <c r="I130" s="15">
+      <c r="I130" s="10"/>
+      <c r="J130" s="15">
         <v>45778</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="30" customHeight="1">
+    <row r="131" spans="1:10" ht="30" customHeight="1">
       <c r="A131" s="10">
         <v>130</v>
       </c>
@@ -5195,11 +5348,12 @@
       <c r="H131" s="10">
         <v>6</v>
       </c>
-      <c r="I131" s="15">
+      <c r="I131" s="10"/>
+      <c r="J131" s="15">
         <v>45778</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="30" customHeight="1">
+    <row r="132" spans="1:10" ht="30" customHeight="1">
       <c r="A132" s="10">
         <v>131</v>
       </c>
@@ -5224,11 +5378,12 @@
       <c r="H132" s="10">
         <v>6</v>
       </c>
-      <c r="I132" s="15">
+      <c r="I132" s="10"/>
+      <c r="J132" s="15">
         <v>45778</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="30" customHeight="1">
+    <row r="133" spans="1:10" ht="30" customHeight="1">
       <c r="A133" s="10">
         <v>132</v>
       </c>
@@ -5243,11 +5398,12 @@
         <v>15</v>
       </c>
       <c r="H133" s="10"/>
-      <c r="I133" s="15">
+      <c r="I133" s="10"/>
+      <c r="J133" s="15">
         <v>45809</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="30" customHeight="1">
+    <row r="134" spans="1:10" ht="30" customHeight="1">
       <c r="A134" s="10">
         <v>133</v>
       </c>
@@ -5262,11 +5418,12 @@
         <v>15</v>
       </c>
       <c r="H134" s="10"/>
-      <c r="I134" s="15">
+      <c r="I134" s="10"/>
+      <c r="J134" s="15">
         <v>45809</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="30" customHeight="1">
+    <row r="135" spans="1:10" ht="30" customHeight="1">
       <c r="A135" s="10">
         <v>134</v>
       </c>
@@ -5281,11 +5438,12 @@
         <v>15</v>
       </c>
       <c r="H135" s="10"/>
-      <c r="I135" s="15">
+      <c r="I135" s="10"/>
+      <c r="J135" s="15">
         <v>45809</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="30" customHeight="1">
+    <row r="136" spans="1:10" ht="30" customHeight="1">
       <c r="A136" s="10">
         <v>135</v>
       </c>
@@ -5300,11 +5458,12 @@
         <v>15</v>
       </c>
       <c r="H136" s="10"/>
-      <c r="I136" s="15">
+      <c r="I136" s="10"/>
+      <c r="J136" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="30" customHeight="1">
+    <row r="137" spans="1:10" ht="30" customHeight="1">
       <c r="A137" s="10">
         <v>136</v>
       </c>
@@ -5319,11 +5478,12 @@
         <v>15</v>
       </c>
       <c r="H137" s="10"/>
-      <c r="I137" s="15">
+      <c r="I137" s="10"/>
+      <c r="J137" s="15">
         <v>46054</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="30" customHeight="1">
+    <row r="138" spans="1:10" ht="30" customHeight="1">
       <c r="A138" s="10">
         <v>137</v>
       </c>
@@ -5338,11 +5498,12 @@
         <v>15</v>
       </c>
       <c r="H138" s="10"/>
-      <c r="I138" s="15">
+      <c r="I138" s="10"/>
+      <c r="J138" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="30" customHeight="1">
+    <row r="139" spans="1:10" ht="30" customHeight="1">
       <c r="A139" s="10">
         <v>138</v>
       </c>
@@ -5357,11 +5518,12 @@
         <v>15</v>
       </c>
       <c r="H139" s="10"/>
-      <c r="I139" s="15">
+      <c r="I139" s="10"/>
+      <c r="J139" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="30" customHeight="1">
+    <row r="140" spans="1:10" ht="30" customHeight="1">
       <c r="A140" s="10">
         <v>139</v>
       </c>
@@ -5376,11 +5538,12 @@
         <v>15</v>
       </c>
       <c r="H140" s="10"/>
-      <c r="I140" s="15">
+      <c r="I140" s="10"/>
+      <c r="J140" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="30" customHeight="1">
+    <row r="141" spans="1:10" ht="30" customHeight="1">
       <c r="A141" s="10">
         <v>140</v>
       </c>
@@ -5395,11 +5558,12 @@
         <v>15</v>
       </c>
       <c r="H141" s="10"/>
-      <c r="I141" s="15">
+      <c r="I141" s="10"/>
+      <c r="J141" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="30" customHeight="1">
+    <row r="142" spans="1:10" ht="30" customHeight="1">
       <c r="A142" s="10">
         <v>141</v>
       </c>
@@ -5414,11 +5578,12 @@
         <v>15</v>
       </c>
       <c r="H142" s="10"/>
-      <c r="I142" s="14">
+      <c r="I142" s="10"/>
+      <c r="J142" s="14">
         <v>45859</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="30" customHeight="1">
+    <row r="143" spans="1:10" ht="30" customHeight="1">
       <c r="A143" s="10">
         <v>142</v>
       </c>
@@ -5435,11 +5600,12 @@
         <v>15</v>
       </c>
       <c r="H143" s="10"/>
-      <c r="I143" s="15">
+      <c r="I143" s="10"/>
+      <c r="J143" s="15">
         <v>45839</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="30" customHeight="1">
+    <row r="144" spans="1:10" ht="30" customHeight="1">
       <c r="A144" s="10">
         <v>143</v>
       </c>
@@ -5454,11 +5620,12 @@
         <v>15</v>
       </c>
       <c r="H144" s="10"/>
-      <c r="I144" s="15">
+      <c r="I144" s="10"/>
+      <c r="J144" s="15">
         <v>45870</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="30" customHeight="1">
+    <row r="145" spans="1:10" ht="30" customHeight="1">
       <c r="A145" s="10">
         <v>144</v>
       </c>
@@ -5473,11 +5640,12 @@
         <v>15</v>
       </c>
       <c r="H145" s="10"/>
-      <c r="I145" s="15">
+      <c r="I145" s="10"/>
+      <c r="J145" s="15">
         <v>45901</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="30" customHeight="1">
+    <row r="146" spans="1:10" ht="30" customHeight="1">
       <c r="A146" s="10">
         <v>145</v>
       </c>
@@ -5492,11 +5660,12 @@
         <v>15</v>
       </c>
       <c r="H146" s="10"/>
-      <c r="I146" s="15">
+      <c r="I146" s="10"/>
+      <c r="J146" s="15">
         <v>45901</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="30" customHeight="1">
+    <row r="147" spans="1:10" ht="30" customHeight="1">
       <c r="A147" s="10">
         <v>146</v>
       </c>
@@ -5513,11 +5682,12 @@
         <v>15</v>
       </c>
       <c r="H147" s="10"/>
-      <c r="I147" s="15">
+      <c r="I147" s="10"/>
+      <c r="J147" s="15">
         <v>45931</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="30" customHeight="1">
+    <row r="148" spans="1:10" ht="30" customHeight="1">
       <c r="A148" s="10">
         <v>147</v>
       </c>
@@ -5532,11 +5702,12 @@
         <v>15</v>
       </c>
       <c r="H148" s="10"/>
-      <c r="I148" s="15">
+      <c r="I148" s="10"/>
+      <c r="J148" s="15">
         <v>45931</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="30" customHeight="1">
+    <row r="149" spans="1:10" ht="30" customHeight="1">
       <c r="A149" s="10">
         <v>148</v>
       </c>
@@ -5551,11 +5722,12 @@
         <v>15</v>
       </c>
       <c r="H149" s="10"/>
-      <c r="I149" s="15">
+      <c r="I149" s="10"/>
+      <c r="J149" s="15">
         <v>46054</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="30" customHeight="1">
+    <row r="150" spans="1:10" ht="30" customHeight="1">
       <c r="A150" s="10">
         <v>149</v>
       </c>
@@ -5570,11 +5742,12 @@
         <v>15</v>
       </c>
       <c r="H150" s="10"/>
-      <c r="I150" s="15">
+      <c r="I150" s="10"/>
+      <c r="J150" s="15">
         <v>46054</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="30" customHeight="1">
+    <row r="151" spans="1:10" ht="30" customHeight="1">
       <c r="A151" s="10">
         <v>150</v>
       </c>
@@ -5589,11 +5762,12 @@
         <v>15</v>
       </c>
       <c r="H151" s="10"/>
-      <c r="I151" s="15">
+      <c r="I151" s="10"/>
+      <c r="J151" s="15">
         <v>46082</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="30" customHeight="1">
+    <row r="152" spans="1:10" ht="30" customHeight="1">
       <c r="A152" s="10">
         <v>151</v>
       </c>
@@ -5608,9 +5782,10 @@
         <v>15</v>
       </c>
       <c r="H152" s="10"/>
-      <c r="I152" s="14"/>
-    </row>
-    <row r="153" spans="1:9" ht="30" customHeight="1">
+      <c r="I152" s="10"/>
+      <c r="J152" s="14"/>
+    </row>
+    <row r="153" spans="1:10" ht="30" customHeight="1">
       <c r="A153" s="10">
         <v>152</v>
       </c>
@@ -5625,9 +5800,10 @@
         <v>15</v>
       </c>
       <c r="H153" s="10"/>
-      <c r="I153" s="14"/>
-    </row>
-    <row r="154" spans="1:9" ht="30" customHeight="1">
+      <c r="I153" s="10"/>
+      <c r="J153" s="14"/>
+    </row>
+    <row r="154" spans="1:10" ht="30" customHeight="1">
       <c r="A154" s="10">
         <v>153</v>
       </c>
@@ -5642,9 +5818,10 @@
         <v>15</v>
       </c>
       <c r="H154" s="10"/>
-      <c r="I154" s="14"/>
-    </row>
-    <row r="155" spans="1:9" ht="30" customHeight="1">
+      <c r="I154" s="10"/>
+      <c r="J154" s="14"/>
+    </row>
+    <row r="155" spans="1:10" ht="30" customHeight="1">
       <c r="A155" s="10">
         <v>154</v>
       </c>
@@ -5659,9 +5836,10 @@
         <v>15</v>
       </c>
       <c r="H155" s="10"/>
-      <c r="I155" s="15"/>
-    </row>
-    <row r="156" spans="1:9" ht="30" customHeight="1">
+      <c r="I155" s="10"/>
+      <c r="J155" s="15"/>
+    </row>
+    <row r="156" spans="1:10" ht="30" customHeight="1">
       <c r="A156" s="10">
         <v>155</v>
       </c>
@@ -5676,9 +5854,10 @@
         <v>15</v>
       </c>
       <c r="H156" s="10"/>
-      <c r="I156" s="15"/>
-    </row>
-    <row r="157" spans="1:9" ht="30" customHeight="1">
+      <c r="I156" s="10"/>
+      <c r="J156" s="15"/>
+    </row>
+    <row r="157" spans="1:10" ht="30" customHeight="1">
       <c r="A157" s="10">
         <v>156</v>
       </c>
@@ -5693,11 +5872,12 @@
         <v>15</v>
       </c>
       <c r="H157" s="10"/>
-      <c r="I157" s="14">
+      <c r="I157" s="10"/>
+      <c r="J157" s="14">
         <v>46080</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="30" customHeight="1">
+    <row r="158" spans="1:10" ht="30" customHeight="1">
       <c r="A158" s="10">
         <v>157</v>
       </c>
@@ -5712,9 +5892,10 @@
         <v>15</v>
       </c>
       <c r="H158" s="10"/>
-      <c r="I158" s="14"/>
-    </row>
-    <row r="159" spans="1:9" ht="30" customHeight="1">
+      <c r="I158" s="10"/>
+      <c r="J158" s="14"/>
+    </row>
+    <row r="159" spans="1:10" ht="30" customHeight="1">
       <c r="A159" s="10">
         <v>158</v>
       </c>
@@ -5729,9 +5910,10 @@
         <v>15</v>
       </c>
       <c r="H159" s="10"/>
-      <c r="I159" s="14"/>
-    </row>
-    <row r="160" spans="1:9" ht="30" customHeight="1">
+      <c r="I159" s="10"/>
+      <c r="J159" s="14"/>
+    </row>
+    <row r="160" spans="1:10" ht="30" customHeight="1">
       <c r="A160" s="10">
         <v>159</v>
       </c>
@@ -5744,9 +5926,10 @@
       <c r="F160" s="10"/>
       <c r="G160" s="11"/>
       <c r="H160" s="10"/>
-      <c r="I160" s="14"/>
-    </row>
-    <row r="161" spans="1:9" ht="30" customHeight="1">
+      <c r="I160" s="10"/>
+      <c r="J160" s="14"/>
+    </row>
+    <row r="161" spans="1:10" ht="30" customHeight="1">
       <c r="A161" s="10">
         <v>160</v>
       </c>
@@ -5759,9 +5942,10 @@
       <c r="F161" s="10"/>
       <c r="G161" s="11"/>
       <c r="H161" s="10"/>
-      <c r="I161" s="14"/>
-    </row>
-    <row r="162" spans="1:9" ht="30" customHeight="1">
+      <c r="I161" s="10"/>
+      <c r="J161" s="14"/>
+    </row>
+    <row r="162" spans="1:10" ht="30" customHeight="1">
       <c r="A162" s="10">
         <v>161</v>
       </c>
@@ -5774,9 +5958,10 @@
       <c r="F162" s="10"/>
       <c r="G162" s="11"/>
       <c r="H162" s="10"/>
-      <c r="I162" s="14"/>
-    </row>
-    <row r="163" spans="1:9" ht="30" customHeight="1">
+      <c r="I162" s="10"/>
+      <c r="J162" s="14"/>
+    </row>
+    <row r="163" spans="1:10" ht="30" customHeight="1">
       <c r="A163" s="10">
         <v>162</v>
       </c>
@@ -5789,9 +5974,10 @@
       <c r="F163" s="10"/>
       <c r="G163" s="11"/>
       <c r="H163" s="10"/>
-      <c r="I163" s="14"/>
-    </row>
-    <row r="164" spans="1:9" ht="30" customHeight="1">
+      <c r="I163" s="10"/>
+      <c r="J163" s="14"/>
+    </row>
+    <row r="164" spans="1:10" ht="30" customHeight="1">
       <c r="A164" s="10">
         <v>163</v>
       </c>
@@ -5804,9 +5990,10 @@
       <c r="F164" s="10"/>
       <c r="G164" s="11"/>
       <c r="H164" s="10"/>
-      <c r="I164" s="14"/>
-    </row>
-    <row r="165" spans="1:9" ht="30" customHeight="1">
+      <c r="I164" s="10"/>
+      <c r="J164" s="14"/>
+    </row>
+    <row r="165" spans="1:10" ht="30" customHeight="1">
       <c r="A165" s="10">
         <v>164</v>
       </c>
@@ -5819,9 +6006,10 @@
       <c r="F165" s="10"/>
       <c r="G165" s="11"/>
       <c r="H165" s="10"/>
-      <c r="I165" s="14"/>
-    </row>
-    <row r="166" spans="1:9" ht="30" customHeight="1">
+      <c r="I165" s="10"/>
+      <c r="J165" s="14"/>
+    </row>
+    <row r="166" spans="1:10" ht="30" customHeight="1">
       <c r="A166" s="10">
         <v>165</v>
       </c>
@@ -5834,9 +6022,10 @@
       <c r="F166" s="10"/>
       <c r="G166" s="11"/>
       <c r="H166" s="10"/>
-      <c r="I166" s="14"/>
-    </row>
-    <row r="167" spans="1:9" ht="30" customHeight="1">
+      <c r="I166" s="10"/>
+      <c r="J166" s="14"/>
+    </row>
+    <row r="167" spans="1:10" ht="30" customHeight="1">
       <c r="A167" s="10">
         <v>166</v>
       </c>
@@ -5849,9 +6038,10 @@
       <c r="F167" s="10"/>
       <c r="G167" s="11"/>
       <c r="H167" s="10"/>
-      <c r="I167" s="14"/>
-    </row>
-    <row r="168" spans="1:9" ht="30" customHeight="1">
+      <c r="I167" s="10"/>
+      <c r="J167" s="14"/>
+    </row>
+    <row r="168" spans="1:10" ht="30" customHeight="1">
       <c r="A168" s="10">
         <v>167</v>
       </c>
@@ -5864,9 +6054,10 @@
       <c r="F168" s="10"/>
       <c r="G168" s="11"/>
       <c r="H168" s="10"/>
-      <c r="I168" s="14"/>
-    </row>
-    <row r="169" spans="1:9" ht="30" customHeight="1">
+      <c r="I168" s="10"/>
+      <c r="J168" s="14"/>
+    </row>
+    <row r="169" spans="1:10" ht="30" customHeight="1">
       <c r="A169" s="10">
         <v>168</v>
       </c>
@@ -5879,9 +6070,10 @@
       <c r="F169" s="10"/>
       <c r="G169" s="11"/>
       <c r="H169" s="10"/>
-      <c r="I169" s="14"/>
-    </row>
-    <row r="170" spans="1:9" ht="30" customHeight="1">
+      <c r="I169" s="10"/>
+      <c r="J169" s="14"/>
+    </row>
+    <row r="170" spans="1:10" ht="30" customHeight="1">
       <c r="A170" s="10">
         <v>169</v>
       </c>
@@ -5894,9 +6086,10 @@
       <c r="F170" s="10"/>
       <c r="G170" s="11"/>
       <c r="H170" s="10"/>
-      <c r="I170" s="14"/>
-    </row>
-    <row r="171" spans="1:9" ht="30" customHeight="1">
+      <c r="I170" s="10"/>
+      <c r="J170" s="14"/>
+    </row>
+    <row r="171" spans="1:10" ht="30" customHeight="1">
       <c r="A171" s="10">
         <v>170</v>
       </c>
@@ -5909,9 +6102,10 @@
       <c r="F171" s="10"/>
       <c r="G171" s="11"/>
       <c r="H171" s="10"/>
-      <c r="I171" s="14"/>
-    </row>
-    <row r="172" spans="1:9" ht="30" customHeight="1">
+      <c r="I171" s="10"/>
+      <c r="J171" s="14"/>
+    </row>
+    <row r="172" spans="1:10" ht="30" customHeight="1">
       <c r="A172" s="10">
         <v>171</v>
       </c>
@@ -5924,9 +6118,10 @@
       <c r="F172" s="10"/>
       <c r="G172" s="11"/>
       <c r="H172" s="10"/>
-      <c r="I172" s="14"/>
-    </row>
-    <row r="173" spans="1:9" ht="30" customHeight="1">
+      <c r="I172" s="10"/>
+      <c r="J172" s="14"/>
+    </row>
+    <row r="173" spans="1:10" ht="30" customHeight="1">
       <c r="A173" s="10">
         <v>172</v>
       </c>
@@ -5939,9 +6134,10 @@
       <c r="F173" s="10"/>
       <c r="G173" s="11"/>
       <c r="H173" s="10"/>
-      <c r="I173" s="14"/>
-    </row>
-    <row r="174" spans="1:9" ht="30" customHeight="1">
+      <c r="I173" s="10"/>
+      <c r="J173" s="14"/>
+    </row>
+    <row r="174" spans="1:10" ht="30" customHeight="1">
       <c r="A174" s="10">
         <v>173</v>
       </c>
@@ -5954,9 +6150,10 @@
       <c r="F174" s="10"/>
       <c r="G174" s="11"/>
       <c r="H174" s="10"/>
-      <c r="I174" s="14"/>
-    </row>
-    <row r="175" spans="1:9" ht="30" customHeight="1">
+      <c r="I174" s="10"/>
+      <c r="J174" s="14"/>
+    </row>
+    <row r="175" spans="1:10" ht="30" customHeight="1">
       <c r="A175" s="10">
         <v>174</v>
       </c>
@@ -5969,9 +6166,10 @@
       <c r="F175" s="10"/>
       <c r="G175" s="11"/>
       <c r="H175" s="10"/>
-      <c r="I175" s="14"/>
-    </row>
-    <row r="176" spans="1:9" ht="30" customHeight="1">
+      <c r="I175" s="10"/>
+      <c r="J175" s="14"/>
+    </row>
+    <row r="176" spans="1:10" ht="30" customHeight="1">
       <c r="A176" s="10">
         <v>175</v>
       </c>
@@ -5984,9 +6182,10 @@
       <c r="F176" s="10"/>
       <c r="G176" s="11"/>
       <c r="H176" s="10"/>
-      <c r="I176" s="14"/>
-    </row>
-    <row r="177" spans="1:9" ht="30" customHeight="1">
+      <c r="I176" s="10"/>
+      <c r="J176" s="14"/>
+    </row>
+    <row r="177" spans="1:10" ht="30" customHeight="1">
       <c r="A177" s="10">
         <v>176</v>
       </c>
@@ -5999,9 +6198,10 @@
       <c r="F177" s="10"/>
       <c r="G177" s="11"/>
       <c r="H177" s="10"/>
-      <c r="I177" s="14"/>
-    </row>
-    <row r="178" spans="1:9" ht="30" customHeight="1">
+      <c r="I177" s="10"/>
+      <c r="J177" s="14"/>
+    </row>
+    <row r="178" spans="1:10" ht="30" customHeight="1">
       <c r="A178" s="10">
         <v>177</v>
       </c>
@@ -6014,9 +6214,10 @@
       <c r="F178" s="10"/>
       <c r="G178" s="11"/>
       <c r="H178" s="10"/>
-      <c r="I178" s="14"/>
-    </row>
-    <row r="179" spans="1:9" ht="30" customHeight="1">
+      <c r="I178" s="10"/>
+      <c r="J178" s="14"/>
+    </row>
+    <row r="179" spans="1:10" ht="30" customHeight="1">
       <c r="A179" s="10">
         <v>178</v>
       </c>
@@ -6029,9 +6230,10 @@
       <c r="F179" s="10"/>
       <c r="G179" s="11"/>
       <c r="H179" s="10"/>
-      <c r="I179" s="14"/>
-    </row>
-    <row r="180" spans="1:9" ht="30" customHeight="1">
+      <c r="I179" s="10"/>
+      <c r="J179" s="14"/>
+    </row>
+    <row r="180" spans="1:10" ht="30" customHeight="1">
       <c r="A180" s="10">
         <v>179</v>
       </c>
@@ -6044,9 +6246,10 @@
       <c r="F180" s="10"/>
       <c r="G180" s="11"/>
       <c r="H180" s="10"/>
-      <c r="I180" s="14"/>
-    </row>
-    <row r="181" spans="1:9" ht="30" customHeight="1">
+      <c r="I180" s="10"/>
+      <c r="J180" s="14"/>
+    </row>
+    <row r="181" spans="1:10" ht="30" customHeight="1">
       <c r="A181" s="10">
         <v>180</v>
       </c>
@@ -6059,9 +6262,10 @@
       <c r="F181" s="10"/>
       <c r="G181" s="11"/>
       <c r="H181" s="10"/>
-      <c r="I181" s="14"/>
-    </row>
-    <row r="182" spans="1:9" ht="30" customHeight="1">
+      <c r="I181" s="10"/>
+      <c r="J181" s="14"/>
+    </row>
+    <row r="182" spans="1:10" ht="30" customHeight="1">
       <c r="A182" s="10">
         <v>181</v>
       </c>
@@ -6074,9 +6278,10 @@
       <c r="F182" s="10"/>
       <c r="G182" s="11"/>
       <c r="H182" s="10"/>
-      <c r="I182" s="14"/>
-    </row>
-    <row r="183" spans="1:9" ht="30" customHeight="1">
+      <c r="I182" s="10"/>
+      <c r="J182" s="14"/>
+    </row>
+    <row r="183" spans="1:10" ht="30" customHeight="1">
       <c r="A183" s="10">
         <v>182</v>
       </c>
@@ -6089,9 +6294,10 @@
       <c r="F183" s="10"/>
       <c r="G183" s="11"/>
       <c r="H183" s="10"/>
-      <c r="I183" s="14"/>
-    </row>
-    <row r="184" spans="1:9" ht="30" customHeight="1">
+      <c r="I183" s="10"/>
+      <c r="J183" s="14"/>
+    </row>
+    <row r="184" spans="1:10" ht="30" customHeight="1">
       <c r="A184" s="10">
         <v>183</v>
       </c>
@@ -6104,9 +6310,10 @@
       <c r="F184" s="10"/>
       <c r="G184" s="11"/>
       <c r="H184" s="10"/>
-      <c r="I184" s="14"/>
-    </row>
-    <row r="185" spans="1:9" ht="30" customHeight="1">
+      <c r="I184" s="10"/>
+      <c r="J184" s="14"/>
+    </row>
+    <row r="185" spans="1:10" ht="30" customHeight="1">
       <c r="A185" s="10">
         <v>184</v>
       </c>
@@ -6119,9 +6326,10 @@
       <c r="F185" s="10"/>
       <c r="G185" s="11"/>
       <c r="H185" s="10"/>
-      <c r="I185" s="14"/>
-    </row>
-    <row r="186" spans="1:9" ht="30" customHeight="1">
+      <c r="I185" s="10"/>
+      <c r="J185" s="14"/>
+    </row>
+    <row r="186" spans="1:10" ht="30" customHeight="1">
       <c r="A186" s="10">
         <v>185</v>
       </c>
@@ -6134,9 +6342,10 @@
       <c r="F186" s="10"/>
       <c r="G186" s="11"/>
       <c r="H186" s="10"/>
-      <c r="I186" s="14"/>
-    </row>
-    <row r="187" spans="1:9" ht="30" customHeight="1">
+      <c r="I186" s="10"/>
+      <c r="J186" s="14"/>
+    </row>
+    <row r="187" spans="1:10" ht="30" customHeight="1">
       <c r="A187" s="10">
         <v>186</v>
       </c>
@@ -6149,9 +6358,10 @@
       <c r="F187" s="10"/>
       <c r="G187" s="11"/>
       <c r="H187" s="10"/>
-      <c r="I187" s="14"/>
-    </row>
-    <row r="188" spans="1:9" ht="30" customHeight="1">
+      <c r="I187" s="10"/>
+      <c r="J187" s="14"/>
+    </row>
+    <row r="188" spans="1:10" ht="30" customHeight="1">
       <c r="A188" s="10">
         <v>187</v>
       </c>
@@ -6164,9 +6374,10 @@
       <c r="F188" s="10"/>
       <c r="G188" s="11"/>
       <c r="H188" s="10"/>
-      <c r="I188" s="14"/>
-    </row>
-    <row r="189" spans="1:9" ht="30" customHeight="1">
+      <c r="I188" s="10"/>
+      <c r="J188" s="14"/>
+    </row>
+    <row r="189" spans="1:10" ht="30" customHeight="1">
       <c r="A189" s="10">
         <v>188</v>
       </c>
@@ -6179,9 +6390,10 @@
       <c r="F189" s="10"/>
       <c r="G189" s="11"/>
       <c r="H189" s="10"/>
-      <c r="I189" s="14"/>
-    </row>
-    <row r="190" spans="1:9" ht="30" customHeight="1">
+      <c r="I189" s="10"/>
+      <c r="J189" s="14"/>
+    </row>
+    <row r="190" spans="1:10" ht="30" customHeight="1">
       <c r="A190" s="10">
         <v>189</v>
       </c>
@@ -6198,9 +6410,10 @@
         <v>15</v>
       </c>
       <c r="H190" s="10"/>
-      <c r="I190" s="14"/>
-    </row>
-    <row r="191" spans="1:9" ht="30" customHeight="1">
+      <c r="I190" s="10"/>
+      <c r="J190" s="14"/>
+    </row>
+    <row r="191" spans="1:10" ht="30" customHeight="1">
       <c r="A191" s="10">
         <v>190</v>
       </c>
@@ -6217,9 +6430,10 @@
         <v>15</v>
       </c>
       <c r="H191" s="10"/>
-      <c r="I191" s="14"/>
-    </row>
-    <row r="192" spans="1:9" ht="30" customHeight="1">
+      <c r="I191" s="10"/>
+      <c r="J191" s="14"/>
+    </row>
+    <row r="192" spans="1:10" ht="30" customHeight="1">
       <c r="A192" s="10">
         <v>191</v>
       </c>
@@ -6236,9 +6450,10 @@
         <v>15</v>
       </c>
       <c r="H192" s="10"/>
-      <c r="I192" s="14"/>
-    </row>
-    <row r="193" spans="1:9" ht="30" customHeight="1">
+      <c r="I192" s="10"/>
+      <c r="J192" s="14"/>
+    </row>
+    <row r="193" spans="1:10" ht="30" customHeight="1">
       <c r="A193" s="10">
         <v>192</v>
       </c>
@@ -6255,9 +6470,10 @@
         <v>15</v>
       </c>
       <c r="H193" s="10"/>
-      <c r="I193" s="14"/>
-    </row>
-    <row r="194" spans="1:9" ht="30" customHeight="1">
+      <c r="I193" s="10"/>
+      <c r="J193" s="14"/>
+    </row>
+    <row r="194" spans="1:10" ht="30" customHeight="1">
       <c r="A194" s="10">
         <v>193</v>
       </c>
@@ -6274,9 +6490,10 @@
         <v>15</v>
       </c>
       <c r="H194" s="10"/>
-      <c r="I194" s="14"/>
-    </row>
-    <row r="195" spans="1:9" ht="30" customHeight="1">
+      <c r="I194" s="10"/>
+      <c r="J194" s="14"/>
+    </row>
+    <row r="195" spans="1:10" ht="30" customHeight="1">
       <c r="A195" s="10">
         <v>194</v>
       </c>
@@ -6293,9 +6510,10 @@
         <v>15</v>
       </c>
       <c r="H195" s="10"/>
-      <c r="I195" s="14"/>
-    </row>
-    <row r="196" spans="1:9" ht="30" customHeight="1">
+      <c r="I195" s="10"/>
+      <c r="J195" s="14"/>
+    </row>
+    <row r="196" spans="1:10" ht="30" customHeight="1">
       <c r="A196" s="10">
         <v>195</v>
       </c>
@@ -6312,9 +6530,10 @@
         <v>15</v>
       </c>
       <c r="H196" s="10"/>
-      <c r="I196" s="14"/>
-    </row>
-    <row r="197" spans="1:9" ht="30" customHeight="1">
+      <c r="I196" s="10"/>
+      <c r="J196" s="14"/>
+    </row>
+    <row r="197" spans="1:10" ht="30" customHeight="1">
       <c r="A197" s="10">
         <v>196</v>
       </c>
@@ -6331,9 +6550,10 @@
         <v>15</v>
       </c>
       <c r="H197" s="10"/>
-      <c r="I197" s="14"/>
-    </row>
-    <row r="198" spans="1:9" ht="30" customHeight="1">
+      <c r="I197" s="10"/>
+      <c r="J197" s="14"/>
+    </row>
+    <row r="198" spans="1:10" ht="30" customHeight="1">
       <c r="A198" s="10">
         <v>197</v>
       </c>
@@ -6350,9 +6570,10 @@
         <v>15</v>
       </c>
       <c r="H198" s="10"/>
-      <c r="I198" s="14"/>
-    </row>
-    <row r="199" spans="1:9" ht="30" customHeight="1">
+      <c r="I198" s="10"/>
+      <c r="J198" s="14"/>
+    </row>
+    <row r="199" spans="1:10" ht="30" customHeight="1">
       <c r="A199" s="10">
         <v>198</v>
       </c>
@@ -6367,9 +6588,10 @@
       <c r="F199" s="10"/>
       <c r="G199" s="11"/>
       <c r="H199" s="10"/>
-      <c r="I199" s="14"/>
-    </row>
-    <row r="200" spans="1:9" ht="30" customHeight="1">
+      <c r="I199" s="10"/>
+      <c r="J199" s="14"/>
+    </row>
+    <row r="200" spans="1:10" ht="30" customHeight="1">
       <c r="A200" s="10">
         <v>199</v>
       </c>
@@ -6384,9 +6606,10 @@
       <c r="F200" s="10"/>
       <c r="G200" s="11"/>
       <c r="H200" s="10"/>
-      <c r="I200" s="14"/>
-    </row>
-    <row r="201" spans="1:9" ht="30" customHeight="1">
+      <c r="I200" s="10"/>
+      <c r="J200" s="14"/>
+    </row>
+    <row r="201" spans="1:10" ht="30" customHeight="1">
       <c r="A201" s="10">
         <v>200</v>
       </c>
@@ -6401,9 +6624,10 @@
       <c r="F201" s="10"/>
       <c r="G201" s="11"/>
       <c r="H201" s="10"/>
-      <c r="I201" s="14"/>
-    </row>
-    <row r="202" spans="1:9" ht="30" customHeight="1">
+      <c r="I201" s="10"/>
+      <c r="J201" s="14"/>
+    </row>
+    <row r="202" spans="1:10" ht="30" customHeight="1">
       <c r="A202" s="10">
         <v>201</v>
       </c>
@@ -6420,9 +6644,10 @@
         <v>15</v>
       </c>
       <c r="H202" s="10"/>
-      <c r="I202" s="14"/>
-    </row>
-    <row r="203" spans="1:9" ht="30" customHeight="1">
+      <c r="I202" s="10"/>
+      <c r="J202" s="14"/>
+    </row>
+    <row r="203" spans="1:10" ht="30" customHeight="1">
       <c r="A203" s="10">
         <v>202</v>
       </c>
@@ -6439,9 +6664,10 @@
         <v>15</v>
       </c>
       <c r="H203" s="10"/>
-      <c r="I203" s="14"/>
-    </row>
-    <row r="204" spans="1:9" ht="30" customHeight="1">
+      <c r="I203" s="10"/>
+      <c r="J203" s="14"/>
+    </row>
+    <row r="204" spans="1:10" ht="30" customHeight="1">
       <c r="A204" s="10">
         <v>203</v>
       </c>
@@ -6458,9 +6684,10 @@
         <v>15</v>
       </c>
       <c r="H204" s="10"/>
-      <c r="I204" s="14"/>
-    </row>
-    <row r="205" spans="1:9" ht="30" customHeight="1">
+      <c r="I204" s="10"/>
+      <c r="J204" s="14"/>
+    </row>
+    <row r="205" spans="1:10" ht="30" customHeight="1">
       <c r="A205" s="10">
         <v>204</v>
       </c>
@@ -6475,9 +6702,10 @@
       <c r="F205" s="10"/>
       <c r="G205" s="11"/>
       <c r="H205" s="10"/>
-      <c r="I205" s="14"/>
-    </row>
-    <row r="206" spans="1:9" ht="30" customHeight="1">
+      <c r="I205" s="10"/>
+      <c r="J205" s="14"/>
+    </row>
+    <row r="206" spans="1:10" ht="30" customHeight="1">
       <c r="A206" s="10">
         <v>205</v>
       </c>
@@ -6492,9 +6720,10 @@
       <c r="F206" s="10"/>
       <c r="G206" s="11"/>
       <c r="H206" s="10"/>
-      <c r="I206" s="14"/>
-    </row>
-    <row r="207" spans="1:9" ht="30" customHeight="1">
+      <c r="I206" s="10"/>
+      <c r="J206" s="14"/>
+    </row>
+    <row r="207" spans="1:10" ht="30" customHeight="1">
       <c r="A207" s="10">
         <v>206</v>
       </c>
@@ -6509,9 +6738,10 @@
       <c r="F207" s="10"/>
       <c r="G207" s="11"/>
       <c r="H207" s="10"/>
-      <c r="I207" s="14"/>
-    </row>
-    <row r="208" spans="1:9" ht="30" customHeight="1">
+      <c r="I207" s="10"/>
+      <c r="J207" s="14"/>
+    </row>
+    <row r="208" spans="1:10" ht="30" customHeight="1">
       <c r="A208" s="10">
         <v>207</v>
       </c>
@@ -6528,9 +6758,10 @@
         <v>15</v>
       </c>
       <c r="H208" s="10"/>
-      <c r="I208" s="14"/>
-    </row>
-    <row r="209" spans="1:9" ht="30" customHeight="1">
+      <c r="I208" s="10"/>
+      <c r="J208" s="14"/>
+    </row>
+    <row r="209" spans="1:10" ht="30" customHeight="1">
       <c r="A209" s="10">
         <v>208</v>
       </c>
@@ -6545,9 +6776,10 @@
       <c r="F209" s="10"/>
       <c r="G209" s="11"/>
       <c r="H209" s="10"/>
-      <c r="I209" s="14"/>
-    </row>
-    <row r="210" spans="1:9" ht="30" customHeight="1">
+      <c r="I209" s="10"/>
+      <c r="J209" s="14"/>
+    </row>
+    <row r="210" spans="1:10" ht="30" customHeight="1">
       <c r="A210" s="10">
         <v>209</v>
       </c>
@@ -6562,9 +6794,10 @@
       <c r="F210" s="10"/>
       <c r="G210" s="11"/>
       <c r="H210" s="10"/>
-      <c r="I210" s="14"/>
-    </row>
-    <row r="211" spans="1:9" ht="30" customHeight="1">
+      <c r="I210" s="10"/>
+      <c r="J210" s="14"/>
+    </row>
+    <row r="211" spans="1:10" ht="30" customHeight="1">
       <c r="A211" s="10">
         <v>210</v>
       </c>
@@ -6579,9 +6812,10 @@
       <c r="F211" s="10"/>
       <c r="G211" s="11"/>
       <c r="H211" s="10"/>
-      <c r="I211" s="14"/>
-    </row>
-    <row r="212" spans="1:9" ht="30" customHeight="1">
+      <c r="I211" s="10"/>
+      <c r="J211" s="14"/>
+    </row>
+    <row r="212" spans="1:10" ht="30" customHeight="1">
       <c r="A212" s="10">
         <v>211</v>
       </c>
@@ -6598,9 +6832,10 @@
         <v>15</v>
       </c>
       <c r="H212" s="10"/>
-      <c r="I212" s="14"/>
-    </row>
-    <row r="213" spans="1:9" ht="30" customHeight="1">
+      <c r="I212" s="10"/>
+      <c r="J212" s="14"/>
+    </row>
+    <row r="213" spans="1:10" ht="30" customHeight="1">
       <c r="A213" s="10">
         <v>212</v>
       </c>
@@ -6615,9 +6850,10 @@
       <c r="F213" s="10"/>
       <c r="G213" s="11"/>
       <c r="H213" s="10"/>
-      <c r="I213" s="14"/>
-    </row>
-    <row r="214" spans="1:9" ht="30" customHeight="1">
+      <c r="I213" s="10"/>
+      <c r="J213" s="14"/>
+    </row>
+    <row r="214" spans="1:10" ht="30" customHeight="1">
       <c r="A214" s="10">
         <v>213</v>
       </c>
@@ -6632,9 +6868,10 @@
       <c r="F214" s="10"/>
       <c r="G214" s="11"/>
       <c r="H214" s="10"/>
-      <c r="I214" s="14"/>
-    </row>
-    <row r="215" spans="1:9" ht="30" customHeight="1">
+      <c r="I214" s="10"/>
+      <c r="J214" s="14"/>
+    </row>
+    <row r="215" spans="1:10" ht="30" customHeight="1">
       <c r="A215" s="10">
         <v>214</v>
       </c>
@@ -6651,9 +6888,10 @@
         <v>15</v>
       </c>
       <c r="H215" s="10"/>
-      <c r="I215" s="14"/>
-    </row>
-    <row r="216" spans="1:9" ht="30" customHeight="1">
+      <c r="I215" s="10"/>
+      <c r="J215" s="14"/>
+    </row>
+    <row r="216" spans="1:10" ht="30" customHeight="1">
       <c r="A216" s="10">
         <v>215</v>
       </c>
@@ -6668,9 +6906,10 @@
       <c r="F216" s="10"/>
       <c r="G216" s="11"/>
       <c r="H216" s="10"/>
-      <c r="I216" s="14"/>
-    </row>
-    <row r="217" spans="1:9" ht="30" customHeight="1">
+      <c r="I216" s="10"/>
+      <c r="J216" s="14"/>
+    </row>
+    <row r="217" spans="1:10" ht="30" customHeight="1">
       <c r="A217" s="10">
         <v>216</v>
       </c>
@@ -6685,9 +6924,10 @@
       <c r="F217" s="10"/>
       <c r="G217" s="11"/>
       <c r="H217" s="10"/>
-      <c r="I217" s="14"/>
-    </row>
-    <row r="218" spans="1:9" ht="30" customHeight="1">
+      <c r="I217" s="10"/>
+      <c r="J217" s="14"/>
+    </row>
+    <row r="218" spans="1:10" ht="30" customHeight="1">
       <c r="A218" s="10">
         <v>217</v>
       </c>
@@ -6702,9 +6942,10 @@
       <c r="F218" s="10"/>
       <c r="G218" s="11"/>
       <c r="H218" s="10"/>
-      <c r="I218" s="14"/>
-    </row>
-    <row r="219" spans="1:9" ht="30" customHeight="1">
+      <c r="I218" s="10"/>
+      <c r="J218" s="14"/>
+    </row>
+    <row r="219" spans="1:10" ht="30" customHeight="1">
       <c r="A219" s="10">
         <v>218</v>
       </c>
@@ -6721,9 +6962,10 @@
       <c r="F219" s="10"/>
       <c r="G219" s="11"/>
       <c r="H219" s="10"/>
-      <c r="I219" s="14"/>
-    </row>
-    <row r="220" spans="1:9" ht="30" customHeight="1">
+      <c r="I219" s="10"/>
+      <c r="J219" s="14"/>
+    </row>
+    <row r="220" spans="1:10" ht="30" customHeight="1">
       <c r="A220" s="10">
         <v>219</v>
       </c>
@@ -6746,13 +6988,16 @@
         <v>15</v>
       </c>
       <c r="H220" s="10">
-        <v>7.1</v>
-      </c>
-      <c r="I220" s="14">
+        <v>7</v>
+      </c>
+      <c r="I220" s="10">
+        <v>7</v>
+      </c>
+      <c r="J220" s="14">
         <v>46200</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="30" customHeight="1">
+    <row r="221" spans="1:10" ht="30" customHeight="1">
       <c r="A221" s="10">
         <v>220</v>
       </c>
@@ -6761,7 +7006,7 @@
       </c>
       <c r="C221" s="11"/>
       <c r="D221" s="16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E221" s="10">
         <v>2026</v>
@@ -6775,20 +7020,23 @@
       <c r="H221" s="10">
         <v>9</v>
       </c>
-      <c r="I221" s="14">
+      <c r="I221" s="10">
+        <v>8</v>
+      </c>
+      <c r="J221" s="14">
         <v>46263</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="30" customHeight="1">
+    <row r="222" spans="1:10" ht="30" customHeight="1">
       <c r="A222" s="10">
         <v>221</v>
       </c>
       <c r="B222" s="16" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C222" s="11"/>
       <c r="D222" s="16" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E222" s="10">
         <v>1989</v>
@@ -6800,22 +7048,25 @@
         <v>15</v>
       </c>
       <c r="H222" s="10">
-        <v>6.9</v>
-      </c>
-      <c r="I222" s="14">
+        <v>7</v>
+      </c>
+      <c r="I222" s="10">
+        <v>8</v>
+      </c>
+      <c r="J222" s="14">
         <v>46300</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="30" customHeight="1">
+    <row r="223" spans="1:10" ht="30" customHeight="1">
       <c r="A223" s="10">
         <v>222</v>
       </c>
       <c r="B223" s="16" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C223" s="11"/>
       <c r="D223" s="16" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E223" s="10">
         <v>2000</v>
@@ -6829,44 +7080,104 @@
       <c r="H223" s="10">
         <v>7.5</v>
       </c>
-      <c r="I223" s="14">
+      <c r="I223" s="10">
+        <v>9</v>
+      </c>
+      <c r="J223" s="14">
         <v>46304</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="30" customHeight="1">
-      <c r="A224" s="10"/>
-      <c r="B224" s="16"/>
+    <row r="224" spans="1:10" ht="30" customHeight="1">
+      <c r="A224" s="10">
+        <v>223</v>
+      </c>
+      <c r="B224" s="16" t="s">
+        <v>420</v>
+      </c>
       <c r="C224" s="11"/>
-      <c r="D224" s="16"/>
-      <c r="E224" s="10"/>
-      <c r="F224" s="10"/>
-      <c r="G224" s="11"/>
-      <c r="H224" s="10"/>
-      <c r="I224" s="14"/>
-    </row>
-    <row r="225" spans="1:9" ht="30" customHeight="1">
-      <c r="A225" s="10"/>
-      <c r="B225" s="16"/>
+      <c r="D224" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="E224" s="10">
+        <v>2004</v>
+      </c>
+      <c r="F224" s="10">
+        <v>8.1</v>
+      </c>
+      <c r="G224" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H224" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="I224" s="10">
+        <v>9</v>
+      </c>
+      <c r="J224" s="14">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="30" customHeight="1">
+      <c r="A225" s="10">
+        <v>224</v>
+      </c>
+      <c r="B225" s="16" t="s">
+        <v>422</v>
+      </c>
       <c r="C225" s="11"/>
-      <c r="D225" s="16"/>
-      <c r="E225" s="10"/>
-      <c r="F225" s="10"/>
-      <c r="G225" s="11"/>
-      <c r="H225" s="10"/>
-      <c r="I225" s="14"/>
-    </row>
-    <row r="226" spans="1:9" ht="30" customHeight="1">
-      <c r="A226" s="10"/>
-      <c r="B226" s="16"/>
+      <c r="D225" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="E225" s="10">
+        <v>2001</v>
+      </c>
+      <c r="F225" s="10">
+        <v>7.9</v>
+      </c>
+      <c r="G225" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H225" s="10">
+        <v>8</v>
+      </c>
+      <c r="I225" s="10">
+        <v>7</v>
+      </c>
+      <c r="J225" s="14">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="30" customHeight="1">
+      <c r="A226" s="10">
+        <v>225</v>
+      </c>
+      <c r="B226" s="16" t="s">
+        <v>425</v>
+      </c>
       <c r="C226" s="11"/>
-      <c r="D226" s="16"/>
-      <c r="E226" s="10"/>
-      <c r="F226" s="10"/>
-      <c r="G226" s="11"/>
-      <c r="H226" s="10"/>
-      <c r="I226" s="14"/>
-    </row>
-    <row r="227" spans="1:9" ht="30" customHeight="1">
+      <c r="D226" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="E226" s="10">
+        <v>1975</v>
+      </c>
+      <c r="F226" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="G226" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H226" s="10">
+        <v>8</v>
+      </c>
+      <c r="I226" s="10">
+        <v>10</v>
+      </c>
+      <c r="J226" s="14">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="30" customHeight="1">
       <c r="A227" s="10"/>
       <c r="B227" s="16"/>
       <c r="C227" s="11"/>
@@ -6875,9 +7186,10 @@
       <c r="F227" s="10"/>
       <c r="G227" s="11"/>
       <c r="H227" s="10"/>
-      <c r="I227" s="14"/>
-    </row>
-    <row r="228" spans="1:9" ht="30" customHeight="1">
+      <c r="I227" s="10"/>
+      <c r="J227" s="14"/>
+    </row>
+    <row r="228" spans="1:10" ht="30" customHeight="1">
       <c r="A228" s="10"/>
       <c r="B228" s="16"/>
       <c r="C228" s="11"/>
@@ -6886,9 +7198,10 @@
       <c r="F228" s="10"/>
       <c r="G228" s="11"/>
       <c r="H228" s="10"/>
-      <c r="I228" s="14"/>
-    </row>
-    <row r="229" spans="1:9" ht="30" customHeight="1">
+      <c r="I228" s="10"/>
+      <c r="J228" s="14"/>
+    </row>
+    <row r="229" spans="1:10" ht="30" customHeight="1">
       <c r="A229" s="10"/>
       <c r="B229" s="16"/>
       <c r="C229" s="11"/>
@@ -6897,9 +7210,10 @@
       <c r="F229" s="10"/>
       <c r="G229" s="11"/>
       <c r="H229" s="10"/>
-      <c r="I229" s="14"/>
-    </row>
-    <row r="230" spans="1:9" ht="30" customHeight="1">
+      <c r="I229" s="10"/>
+      <c r="J229" s="14"/>
+    </row>
+    <row r="230" spans="1:10" ht="30" customHeight="1">
       <c r="A230" s="10"/>
       <c r="B230" s="16"/>
       <c r="C230" s="11"/>
@@ -6908,9 +7222,10 @@
       <c r="F230" s="10"/>
       <c r="G230" s="11"/>
       <c r="H230" s="10"/>
-      <c r="I230" s="14"/>
-    </row>
-    <row r="231" spans="1:9" ht="30" customHeight="1">
+      <c r="I230" s="10"/>
+      <c r="J230" s="14"/>
+    </row>
+    <row r="231" spans="1:10" ht="30" customHeight="1">
       <c r="A231" s="10"/>
       <c r="B231" s="16"/>
       <c r="C231" s="11"/>
@@ -6919,9 +7234,10 @@
       <c r="F231" s="10"/>
       <c r="G231" s="11"/>
       <c r="H231" s="10"/>
-      <c r="I231" s="14"/>
-    </row>
-    <row r="232" spans="1:9" ht="30" customHeight="1">
+      <c r="I231" s="10"/>
+      <c r="J231" s="14"/>
+    </row>
+    <row r="232" spans="1:10" ht="30" customHeight="1">
       <c r="A232" s="10"/>
       <c r="B232" s="16"/>
       <c r="C232" s="11"/>
@@ -6930,9 +7246,10 @@
       <c r="F232" s="10"/>
       <c r="G232" s="11"/>
       <c r="H232" s="10"/>
-      <c r="I232" s="14"/>
-    </row>
-    <row r="233" spans="1:9" ht="30" customHeight="1">
+      <c r="I232" s="10"/>
+      <c r="J232" s="14"/>
+    </row>
+    <row r="233" spans="1:10" ht="30" customHeight="1">
       <c r="A233" s="10"/>
       <c r="B233" s="16"/>
       <c r="C233" s="11"/>
@@ -6941,9 +7258,10 @@
       <c r="F233" s="10"/>
       <c r="G233" s="11"/>
       <c r="H233" s="10"/>
-      <c r="I233" s="14"/>
-    </row>
-    <row r="234" spans="1:9" ht="30" customHeight="1">
+      <c r="I233" s="10"/>
+      <c r="J233" s="14"/>
+    </row>
+    <row r="234" spans="1:10" ht="30" customHeight="1">
       <c r="A234" s="10"/>
       <c r="B234" s="16"/>
       <c r="C234" s="11"/>
@@ -6952,9 +7270,10 @@
       <c r="F234" s="10"/>
       <c r="G234" s="11"/>
       <c r="H234" s="10"/>
-      <c r="I234" s="14"/>
-    </row>
-    <row r="235" spans="1:9" ht="30" customHeight="1">
+      <c r="I234" s="10"/>
+      <c r="J234" s="14"/>
+    </row>
+    <row r="235" spans="1:10" ht="30" customHeight="1">
       <c r="A235" s="10"/>
       <c r="B235" s="16"/>
       <c r="C235" s="11"/>
@@ -6963,9 +7282,10 @@
       <c r="F235" s="10"/>
       <c r="G235" s="11"/>
       <c r="H235" s="10"/>
-      <c r="I235" s="14"/>
-    </row>
-    <row r="236" spans="1:9" ht="30" customHeight="1">
+      <c r="I235" s="10"/>
+      <c r="J235" s="14"/>
+    </row>
+    <row r="236" spans="1:10" ht="30" customHeight="1">
       <c r="A236" s="10"/>
       <c r="B236" s="16"/>
       <c r="C236" s="11"/>
@@ -6974,9 +7294,10 @@
       <c r="F236" s="10"/>
       <c r="G236" s="11"/>
       <c r="H236" s="10"/>
-      <c r="I236" s="14"/>
-    </row>
-    <row r="237" spans="1:9" ht="30" customHeight="1">
+      <c r="I236" s="10"/>
+      <c r="J236" s="14"/>
+    </row>
+    <row r="237" spans="1:10" ht="30" customHeight="1">
       <c r="A237" s="10"/>
       <c r="B237" s="16"/>
       <c r="C237" s="11"/>
@@ -6985,9 +7306,10 @@
       <c r="F237" s="10"/>
       <c r="G237" s="11"/>
       <c r="H237" s="10"/>
-      <c r="I237" s="14"/>
-    </row>
-    <row r="238" spans="1:9" ht="30" customHeight="1">
+      <c r="I237" s="10"/>
+      <c r="J237" s="14"/>
+    </row>
+    <row r="238" spans="1:10" ht="30" customHeight="1">
       <c r="A238" s="10"/>
       <c r="B238" s="16"/>
       <c r="C238" s="11"/>
@@ -6996,9 +7318,10 @@
       <c r="F238" s="10"/>
       <c r="G238" s="11"/>
       <c r="H238" s="10"/>
-      <c r="I238" s="14"/>
-    </row>
-    <row r="239" spans="1:9" ht="30" customHeight="1">
+      <c r="I238" s="10"/>
+      <c r="J238" s="14"/>
+    </row>
+    <row r="239" spans="1:10" ht="30" customHeight="1">
       <c r="A239" s="10"/>
       <c r="B239" s="16"/>
       <c r="C239" s="11"/>
@@ -7007,9 +7330,10 @@
       <c r="F239" s="10"/>
       <c r="G239" s="11"/>
       <c r="H239" s="10"/>
-      <c r="I239" s="14"/>
-    </row>
-    <row r="240" spans="1:9" ht="30" customHeight="1">
+      <c r="I239" s="10"/>
+      <c r="J239" s="14"/>
+    </row>
+    <row r="240" spans="1:10" ht="30" customHeight="1">
       <c r="A240" s="10"/>
       <c r="B240" s="16"/>
       <c r="C240" s="11"/>
@@ -7018,9 +7342,10 @@
       <c r="F240" s="10"/>
       <c r="G240" s="11"/>
       <c r="H240" s="10"/>
-      <c r="I240" s="14"/>
-    </row>
-    <row r="241" spans="1:9" ht="30" customHeight="1">
+      <c r="I240" s="10"/>
+      <c r="J240" s="14"/>
+    </row>
+    <row r="241" spans="1:10" ht="30" customHeight="1">
       <c r="A241" s="10"/>
       <c r="B241" s="16"/>
       <c r="C241" s="11"/>
@@ -7029,9 +7354,10 @@
       <c r="F241" s="10"/>
       <c r="G241" s="11"/>
       <c r="H241" s="10"/>
-      <c r="I241" s="14"/>
-    </row>
-    <row r="242" spans="1:9" ht="30" customHeight="1">
+      <c r="I241" s="10"/>
+      <c r="J241" s="14"/>
+    </row>
+    <row r="242" spans="1:10" ht="30" customHeight="1">
       <c r="A242" s="10"/>
       <c r="B242" s="16"/>
       <c r="C242" s="11"/>
@@ -7040,20 +7366,21 @@
       <c r="F242" s="10"/>
       <c r="G242" s="11"/>
       <c r="H242" s="10"/>
-      <c r="I242" s="14"/>
+      <c r="I242" s="10"/>
+      <c r="J242" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I221">
+  <autoFilter ref="A1:J221">
     <sortState ref="A2:I222">
       <sortCondition ref="A1:A221"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A2:I222">
+  <conditionalFormatting sqref="A2:J222">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$G2="Просмотрен"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A223:I242">
+  <conditionalFormatting sqref="A223:J242">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G223="Просмотрен"</formula>
     </cfRule>
@@ -7914,15 +8241,17 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C33" s="33" t="s">
         <v>383</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>416</v>
-      </c>
-      <c r="E33" s="7"/>
+        <v>414</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>426</v>
+      </c>
       <c r="F33" s="5">
         <v>2026</v>
       </c>
@@ -7934,15 +8263,17 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1">
-      <c r="A34" s="28"/>
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
       <c r="B34" s="33" t="s">
-        <v>371</v>
+        <v>427</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>370</v>
+        <v>429</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="5"/>
@@ -7950,15 +8281,17 @@
       <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1">
-      <c r="A35" s="5"/>
-      <c r="B35" s="7" t="s">
-        <v>372</v>
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>428</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>374</v>
+        <v>320</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="5"/>
@@ -7966,49 +8299,49 @@
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1">
-      <c r="A36" s="5"/>
-      <c r="B36" s="31" t="s">
-        <v>376</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>375</v>
-      </c>
-      <c r="D36" s="31" t="s">
+      <c r="A36" s="28"/>
+      <c r="B36" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="D36" s="33" t="s">
         <v>344</v>
       </c>
-      <c r="E36" s="34"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1">
       <c r="A37" s="5"/>
-      <c r="B37" s="31" t="s">
-        <v>381</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
+      <c r="B37" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1">
       <c r="A38" s="5"/>
       <c r="B38" s="31" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D38" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="E38" s="35"/>
+      <c r="E38" s="34"/>
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
       <c r="H38" s="35"/>
@@ -8016,13 +8349,13 @@
     <row r="39" spans="1:8" ht="30" customHeight="1">
       <c r="A39" s="5"/>
       <c r="B39" s="31" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="E39" s="35"/>
       <c r="F39" s="35"/>
@@ -8032,13 +8365,13 @@
     <row r="40" spans="1:8" ht="30" customHeight="1">
       <c r="A40" s="5"/>
       <c r="B40" s="31" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="E40" s="35"/>
       <c r="F40" s="35"/>
@@ -8048,7 +8381,7 @@
     <row r="41" spans="1:8" ht="30" customHeight="1">
       <c r="A41" s="5"/>
       <c r="B41" s="31" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C41" s="31" t="s">
         <v>356</v>
@@ -8064,7 +8397,7 @@
     <row r="42" spans="1:8" ht="30" customHeight="1">
       <c r="A42" s="5"/>
       <c r="B42" s="31" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C42" s="31" t="s">
         <v>356</v>
@@ -8080,7 +8413,7 @@
     <row r="43" spans="1:8" ht="30" customHeight="1">
       <c r="A43" s="5"/>
       <c r="B43" s="31" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C43" s="31" t="s">
         <v>356</v>
@@ -8096,7 +8429,7 @@
     <row r="44" spans="1:8" ht="30" customHeight="1">
       <c r="A44" s="5"/>
       <c r="B44" s="31" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C44" s="31" t="s">
         <v>356</v>
@@ -8112,7 +8445,7 @@
     <row r="45" spans="1:8" ht="30" customHeight="1">
       <c r="A45" s="5"/>
       <c r="B45" s="31" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C45" s="31" t="s">
         <v>356</v>
@@ -8128,7 +8461,7 @@
     <row r="46" spans="1:8" ht="30" customHeight="1">
       <c r="A46" s="5"/>
       <c r="B46" s="31" t="s">
-        <v>257</v>
+        <v>394</v>
       </c>
       <c r="C46" s="31" t="s">
         <v>356</v>
@@ -8144,13 +8477,13 @@
     <row r="47" spans="1:8" ht="30" customHeight="1">
       <c r="A47" s="5"/>
       <c r="B47" s="31" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C47" s="31" t="s">
         <v>356</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="E47" s="35"/>
       <c r="F47" s="35"/>
@@ -8160,13 +8493,13 @@
     <row r="48" spans="1:8" ht="30" customHeight="1">
       <c r="A48" s="5"/>
       <c r="B48" s="31" t="s">
-        <v>48</v>
+        <v>257</v>
       </c>
       <c r="C48" s="31" t="s">
         <v>356</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="E48" s="35"/>
       <c r="F48" s="35"/>
@@ -8176,7 +8509,7 @@
     <row r="49" spans="1:8" ht="30" customHeight="1">
       <c r="A49" s="5"/>
       <c r="B49" s="31" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C49" s="31" t="s">
         <v>356</v>
@@ -8191,45 +8524,45 @@
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1">
       <c r="A50" s="5"/>
-      <c r="B50" s="41" t="s">
-        <v>409</v>
-      </c>
-      <c r="C50" s="40" t="s">
-        <v>408</v>
-      </c>
-      <c r="D50" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
+      <c r="B50" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>397</v>
+      </c>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35"/>
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1">
       <c r="A51" s="5"/>
-      <c r="B51" s="41" t="s">
-        <v>410</v>
-      </c>
-      <c r="C51" s="40" t="s">
-        <v>408</v>
-      </c>
-      <c r="D51" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
+      <c r="B51" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="C51" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="D51" s="31" t="s">
+        <v>397</v>
+      </c>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1">
       <c r="A52" s="5"/>
-      <c r="B52" s="41" t="s">
-        <v>411</v>
-      </c>
-      <c r="C52" s="40" t="s">
-        <v>380</v>
-      </c>
-      <c r="D52" s="40" t="s">
+      <c r="B52" s="37" t="s">
+        <v>407</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>406</v>
+      </c>
+      <c r="D52" s="36" t="s">
         <v>344</v>
       </c>
       <c r="E52" s="7"/>
@@ -8239,13 +8572,13 @@
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1">
       <c r="A53" s="5"/>
-      <c r="B53" s="31" t="s">
-        <v>379</v>
-      </c>
-      <c r="C53" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="D53" s="31" t="s">
+      <c r="B53" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="C53" s="36" t="s">
+        <v>406</v>
+      </c>
+      <c r="D53" s="36" t="s">
         <v>344</v>
       </c>
       <c r="E53" s="7"/>
@@ -8254,14 +8587,14 @@
       <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1">
-      <c r="A54" s="42"/>
-      <c r="B54" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="C54" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="D54" s="31" t="s">
+      <c r="A54" s="5"/>
+      <c r="B54" s="37" t="s">
+        <v>409</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="D54" s="36" t="s">
         <v>344</v>
       </c>
       <c r="E54" s="7"/>
@@ -8272,10 +8605,10 @@
     <row r="55" spans="1:8" ht="30" customHeight="1">
       <c r="A55" s="5"/>
       <c r="B55" s="31" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C55" s="31" t="s">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="D55" s="31" t="s">
         <v>344</v>
@@ -8286,14 +8619,14 @@
       <c r="H55" s="5"/>
     </row>
     <row r="56" spans="1:8" ht="30" customHeight="1">
-      <c r="A56" s="5"/>
-      <c r="B56" s="40" t="s">
-        <v>412</v>
+      <c r="A56" s="38"/>
+      <c r="B56" s="31" t="s">
+        <v>377</v>
       </c>
       <c r="C56" s="31" t="s">
-        <v>383</v>
-      </c>
-      <c r="D56" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="D56" s="31" t="s">
         <v>344</v>
       </c>
       <c r="E56" s="7"/>
@@ -8303,13 +8636,13 @@
     </row>
     <row r="57" spans="1:8" ht="30" customHeight="1">
       <c r="A57" s="5"/>
-      <c r="B57" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="D57" s="40" t="s">
+      <c r="B57" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="C57" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="D57" s="31" t="s">
         <v>344</v>
       </c>
       <c r="E57" s="7"/>
@@ -8319,13 +8652,13 @@
     </row>
     <row r="58" spans="1:8" ht="30" customHeight="1">
       <c r="A58" s="5"/>
-      <c r="B58" s="40" t="s">
-        <v>413</v>
-      </c>
-      <c r="C58" s="40" t="s">
+      <c r="B58" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="C58" s="36" t="s">
         <v>366</v>
       </c>
-      <c r="D58" s="40" t="s">
+      <c r="D58" s="36" t="s">
         <v>344</v>
       </c>
       <c r="E58" s="7"/>
@@ -8335,9 +8668,9 @@
     </row>
     <row r="59" spans="1:8" ht="30" customHeight="1">
       <c r="A59" s="5"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="40"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
       <c r="E59" s="7"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -8369,282 +8702,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="2" width="9.140625" style="8"/>
-    <col min="3" max="3" width="19.85546875" style="8" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>406</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="37">
-        <v>46271</v>
-      </c>
-      <c r="C2">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="37">
-        <v>46272</v>
-      </c>
-      <c r="C3">
-        <f>C2+20</f>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="37">
-        <v>46273</v>
-      </c>
-      <c r="C4">
-        <f>C3+20</f>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="37">
-        <v>46274</v>
-      </c>
-      <c r="C5">
-        <f>C4+20</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="37">
-        <v>46275</v>
-      </c>
-      <c r="C6">
-        <f t="shared" ref="C6:C20" si="0">C5+20</f>
-        <v>320</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="37">
-        <v>46276</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="37">
-        <v>46277</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>360</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="37">
-        <v>46278</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="37">
-        <v>46279</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="37">
-        <v>46280</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>420</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="37">
-        <v>46281</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="0"/>
-        <v>440</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="37">
-        <v>46282</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>460</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="0"/>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="37">
-        <v>46284</v>
-      </c>
-      <c r="C15">
-        <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="37">
-        <v>46285</v>
-      </c>
-      <c r="C16">
-        <f t="shared" si="0"/>
-        <v>520</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="37">
-        <v>46286</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>540</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="37">
-        <v>46287</v>
-      </c>
-      <c r="C18">
-        <f t="shared" si="0"/>
-        <v>560</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="37">
-        <v>46288</v>
-      </c>
-      <c r="C19">
-        <f t="shared" si="0"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="37">
-        <v>46289</v>
-      </c>
-      <c r="C20">
-        <f t="shared" si="0"/>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="37">
-        <v>46290</v>
-      </c>
-      <c r="C21">
-        <f>C20+20</f>
-        <v>620</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="38">
-        <v>21</v>
-      </c>
-      <c r="B22" s="39">
-        <v>46291</v>
-      </c>
-      <c r="C22" s="38">
-        <v>637</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
@@ -8653,7 +8710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -8923,7 +8980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8933,201 +8990,209 @@
     <col min="3" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="44" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:4" s="40" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="45" t="s">
-        <v>414</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>415</v>
+      <c r="C1" s="41" t="s">
+        <v>412</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="43">
+      <c r="A2" s="39">
         <v>1</v>
       </c>
-      <c r="B2" s="46">
+      <c r="B2" s="42">
         <v>46289</v>
       </c>
-      <c r="C2" s="47">
+      <c r="C2" s="43">
         <v>3.9583333333333331E-2</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="43">
         <v>8.4722222222222213E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
+      <c r="A3" s="39">
+        <v>2</v>
+      </c>
+      <c r="B3" s="42">
+        <v>46313</v>
+      </c>
+      <c r="C3" s="43">
+        <v>4.3055555555555562E-2</v>
+      </c>
+      <c r="D3" s="43">
+        <v>7.1527777777777787E-2</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4"/>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
+      <c r="A5" s="39"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7"/>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8"/>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9"/>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10"/>
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12"/>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
+      <c r="A12" s="39"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24"/>
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
+      <c r="A25" s="39"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
+      <c r="A29" s="39"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
@@ -22,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Кино!$A$1:$J$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Книги!$A$1:$H$60</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="434">
   <si>
     <t>№</t>
   </si>
@@ -1349,12 +1344,19 @@
   </si>
   <si>
     <t>Оценка Ани</t>
+  </si>
+  <si>
+    <t>Жим лежа
+70 кг 2 по 8</t>
+  </si>
+  <si>
+    <t>Скручивания на наклонной скамье 2 по 15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
@@ -1420,7 +1422,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1460,6 +1462,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1547,7 +1555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1679,6 +1687,18 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1761,7 +1781,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1793,10 +1813,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1828,7 +1847,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2004,7 +2022,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J242"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -6074,20 +6092,20 @@
       <c r="J169" s="14"/>
     </row>
     <row r="170" spans="1:10" ht="30" customHeight="1">
-      <c r="A170" s="10">
+      <c r="A170" s="47">
         <v>169</v>
       </c>
-      <c r="B170" s="16"/>
-      <c r="C170" s="11"/>
-      <c r="D170" s="16" t="s">
+      <c r="B170" s="48"/>
+      <c r="C170" s="49"/>
+      <c r="D170" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="E170" s="10"/>
-      <c r="F170" s="10"/>
-      <c r="G170" s="11"/>
-      <c r="H170" s="10"/>
-      <c r="I170" s="10"/>
-      <c r="J170" s="14"/>
+      <c r="E170" s="47"/>
+      <c r="F170" s="47"/>
+      <c r="G170" s="49"/>
+      <c r="H170" s="47"/>
+      <c r="I170" s="47"/>
+      <c r="J170" s="50"/>
     </row>
     <row r="171" spans="1:10" ht="30" customHeight="1">
       <c r="A171" s="10">
@@ -7391,7 +7409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -8701,7 +8719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
@@ -8711,7 +8729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -8915,12 +8933,20 @@
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="B8" s="25">
+        <v>46314</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>284</v>
+      </c>
       <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>433</v>
+      </c>
       <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>432</v>
+      </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -8981,7 +9007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9033,10 +9059,18 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="39"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
+      <c r="A4" s="39">
+        <v>3</v>
+      </c>
+      <c r="B4" s="42">
+        <v>46315</v>
+      </c>
+      <c r="C4" s="43">
+        <v>4.2361111111111106E-2</v>
+      </c>
+      <c r="D4" s="43">
+        <v>0.10625</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="39"/>

--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -9073,10 +9073,18 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="39"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
+      <c r="A5" s="39">
+        <v>4</v>
+      </c>
+      <c r="B5" s="42">
+        <v>46316</v>
+      </c>
+      <c r="C5" s="43">
+        <v>3.6805555555555557E-2</v>
+      </c>
+      <c r="D5" s="43">
+        <v>7.7083333333333337E-2</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="39"/>

--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -9087,10 +9087,18 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="39"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="A6" s="39">
+        <v>5</v>
+      </c>
+      <c r="B6" s="42">
+        <v>46317</v>
+      </c>
+      <c r="C6" s="43">
+        <v>3.4027777777777775E-2</v>
+      </c>
+      <c r="D6" s="43">
+        <v>6.805555555555555E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="39"/>

--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980"/>
   </bookViews>
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
@@ -9101,10 +9101,18 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="39"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="A7" s="39">
+        <v>6</v>
+      </c>
+      <c r="B7" s="42">
+        <v>46318</v>
+      </c>
+      <c r="C7" s="43">
+        <v>3.2638888888888891E-2</v>
+      </c>
+      <c r="D7" s="43">
+        <v>8.2638888888888887E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="39"/>

--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\2026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
@@ -1356,7 +1361,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
@@ -1391,18 +1396,21 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Cascadia Mono SemiBold"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Bahnschrift SemiBold"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Bahnschrift"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
@@ -1781,7 +1789,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1813,9 +1821,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1847,6 +1856,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2022,7 +2032,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J242"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -7409,7 +7419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -8719,7 +8729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
@@ -8729,7 +8739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -9007,7 +9017,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9115,10 +9125,18 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="39"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
+      <c r="A8" s="39">
+        <v>7</v>
+      </c>
+      <c r="B8" s="42">
+        <v>46320</v>
+      </c>
+      <c r="C8" s="43">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="D8" s="43">
+        <v>7.3611111111111113E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="39"/>

--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="4"/>
   </bookViews>
@@ -40,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="437">
   <si>
     <t>№</t>
   </si>
@@ -1356,12 +1351,21 @@
   </si>
   <si>
     <t>Скручивания на наклонной скамье 2 по 15</t>
+  </si>
+  <si>
+    <t>Выспался или нет</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>Да</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
@@ -1563,7 +1567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1707,6 +1711,9 @@
     <xf numFmtId="165" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1789,7 +1796,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1821,10 +1828,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1856,7 +1862,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2032,7 +2037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J242"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -7419,7 +7424,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -8729,7 +8734,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
@@ -8739,7 +8744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -9017,16 +9022,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="8"/>
     <col min="2" max="2" width="10.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="8"/>
+    <col min="3" max="4" width="9.140625" style="8"/>
+    <col min="5" max="5" width="15.85546875" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="40" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:5" s="40" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -9039,8 +9046,11 @@
       <c r="D1" s="41" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="51" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="39">
         <v>1</v>
       </c>
@@ -9053,8 +9063,9 @@
       <c r="D2" s="43">
         <v>8.4722222222222213E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="43"/>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="39">
         <v>2</v>
       </c>
@@ -9067,8 +9078,9 @@
       <c r="D3" s="43">
         <v>7.1527777777777787E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="43"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="39">
         <v>3</v>
       </c>
@@ -9081,8 +9093,11 @@
       <c r="D4" s="43">
         <v>0.10625</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="43" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="39">
         <v>4</v>
       </c>
@@ -9095,8 +9110,11 @@
       <c r="D5" s="43">
         <v>7.7083333333333337E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="43" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="39">
         <v>5</v>
       </c>
@@ -9109,8 +9127,11 @@
       <c r="D6" s="43">
         <v>6.805555555555555E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="43" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="39">
         <v>6</v>
       </c>
@@ -9123,8 +9144,11 @@
       <c r="D7" s="43">
         <v>8.2638888888888887E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="43" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="39">
         <v>7</v>
       </c>
@@ -9137,138 +9161,203 @@
       <c r="D8" s="43">
         <v>7.3611111111111113E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="39"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="39"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="39"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="39"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E8" s="43" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="39">
+        <v>8</v>
+      </c>
+      <c r="B9" s="42">
+        <v>46322</v>
+      </c>
+      <c r="C9" s="43">
+        <v>3.6805555555555557E-2</v>
+      </c>
+      <c r="D9" s="43">
+        <v>9.0972222222222218E-2</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="39">
+        <v>9</v>
+      </c>
+      <c r="B10" s="42">
+        <v>46322</v>
+      </c>
+      <c r="C10" s="43">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D10" s="43">
+        <v>9.8611111111111108E-2</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="39">
+        <v>10</v>
+      </c>
+      <c r="B11" s="42">
+        <v>46323</v>
+      </c>
+      <c r="C11" s="43">
+        <v>3.1944444444444449E-2</v>
+      </c>
+      <c r="D11" s="43">
+        <v>8.6805555555555566E-2</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="39">
+        <v>11</v>
+      </c>
+      <c r="B12" s="42">
+        <v>46324</v>
+      </c>
+      <c r="C12" s="43">
+        <v>2.7083333333333334E-2</v>
+      </c>
+      <c r="D12" s="43">
+        <v>7.9861111111111105E-2</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="39"/>
       <c r="B13" s="42"/>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="43"/>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="39"/>
       <c r="B14" s="42"/>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="43"/>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="39"/>
       <c r="B15" s="42"/>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="43"/>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="39"/>
       <c r="B16" s="42"/>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="43"/>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="39"/>
       <c r="B17" s="42"/>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="43"/>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="39"/>
       <c r="B18" s="42"/>
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="43"/>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="39"/>
       <c r="B19" s="42"/>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="43"/>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="39"/>
       <c r="B20" s="42"/>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="43"/>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="39"/>
       <c r="B21" s="42"/>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="43"/>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="39"/>
       <c r="B22" s="42"/>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="43"/>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="39"/>
       <c r="B23" s="42"/>
       <c r="C23" s="43"/>
       <c r="D23" s="43"/>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="43"/>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="39"/>
       <c r="B24" s="42"/>
       <c r="C24" s="43"/>
       <c r="D24" s="43"/>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="43"/>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="39"/>
       <c r="B25" s="42"/>
       <c r="C25" s="43"/>
       <c r="D25" s="43"/>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="43"/>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="39"/>
       <c r="B26" s="42"/>
       <c r="C26" s="43"/>
       <c r="D26" s="43"/>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="43"/>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
       <c r="C27" s="43"/>
       <c r="D27" s="43"/>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="43"/>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="39"/>
       <c r="B28" s="42"/>
       <c r="C28" s="43"/>
       <c r="D28" s="43"/>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="43"/>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="39"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43"/>
       <c r="D29" s="43"/>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="43"/>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="39"/>
       <c r="B30" s="42"/>
       <c r="C30" s="43"/>
       <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/2026/Кино-Книги-Одежда-Спорт.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="440">
   <si>
     <t>№</t>
   </si>
@@ -1360,6 +1360,15 @@
   </si>
   <si>
     <t>Да</t>
+  </si>
+  <si>
+    <t>Вс</t>
+  </si>
+  <si>
+    <t>Ср</t>
+  </si>
+  <si>
+    <t>Пт</t>
   </si>
 </sst>
 </file>
@@ -1372,11 +1381,19 @@
     <numFmt numFmtId="166" formatCode="mmm\.yy"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -1433,8 +1450,16 @@
       <name val="Antique Olive Compact"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1480,6 +1505,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1567,13 +1598,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1589,50 +1620,50 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1641,22 +1672,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1666,22 +1697,22 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1690,29 +1721,41 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8296,40 +8339,40 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1">
-      <c r="A34" s="5">
+      <c r="A34" s="52">
         <v>33</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="53" t="s">
         <v>427</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="53" t="s">
         <v>429</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D34" s="53" t="s">
         <v>374</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1">
-      <c r="A35" s="5">
+      <c r="A35" s="52">
         <v>34</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="53" t="s">
         <v>428</v>
       </c>
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="53" t="s">
         <v>430</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D35" s="53" t="s">
         <v>320</v>
       </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1">
       <c r="A36" s="28"/>
@@ -9023,341 +9066,408 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="8"/>
     <col min="2" max="2" width="10.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="8"/>
-    <col min="5" max="5" width="15.85546875" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="8"/>
+    <col min="3" max="3" width="10.140625" style="8" customWidth="1"/>
+    <col min="4" max="5" width="9.140625" style="8"/>
+    <col min="6" max="6" width="15.85546875" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="40" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:6" s="40" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="51" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1" s="41" t="s">
         <v>412</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="E1" s="41" t="s">
         <v>413</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="F1" s="51" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="39">
         <v>1</v>
       </c>
       <c r="B2" s="42">
         <v>46289</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="43">
         <v>3.9583333333333331E-2</v>
       </c>
-      <c r="D2" s="43">
+      <c r="E2" s="43">
         <v>8.4722222222222213E-2</v>
       </c>
-      <c r="E2" s="43"/>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="43"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="39">
         <v>2</v>
       </c>
       <c r="B3" s="42">
         <v>46313</v>
       </c>
-      <c r="C3" s="43">
+      <c r="C3" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D3" s="43">
         <v>4.3055555555555562E-2</v>
       </c>
-      <c r="D3" s="43">
+      <c r="E3" s="43">
         <v>7.1527777777777787E-2</v>
       </c>
-      <c r="E3" s="43"/>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="39">
         <v>3</v>
       </c>
       <c r="B4" s="42">
         <v>46315</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" s="43">
         <v>4.2361111111111106E-2</v>
       </c>
-      <c r="D4" s="43">
+      <c r="E4" s="43">
         <v>0.10625</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="F4" s="43" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="39">
         <v>4</v>
       </c>
       <c r="B5" s="42">
         <v>46316</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" s="43">
         <v>3.6805555555555557E-2</v>
       </c>
-      <c r="D5" s="43">
+      <c r="E5" s="43">
         <v>7.7083333333333337E-2</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="F5" s="43" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="39">
         <v>5</v>
       </c>
       <c r="B6" s="42">
         <v>46317</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="43">
         <v>3.4027777777777775E-2</v>
       </c>
-      <c r="D6" s="43">
+      <c r="E6" s="43">
         <v>6.805555555555555E-2</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="F6" s="43" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" s="39">
         <v>6</v>
       </c>
       <c r="B7" s="42">
         <v>46318</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="D7" s="43">
         <v>3.2638888888888891E-2</v>
       </c>
-      <c r="D7" s="43">
+      <c r="E7" s="43">
         <v>8.2638888888888887E-2</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="F7" s="43" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" s="39">
         <v>7</v>
       </c>
       <c r="B8" s="42">
         <v>46320</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="43">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="D8" s="43">
+      <c r="E8" s="43">
         <v>7.3611111111111113E-2</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="F8" s="43" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="39">
         <v>8</v>
       </c>
       <c r="B9" s="42">
         <v>46322</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="43">
         <v>3.6805555555555557E-2</v>
       </c>
-      <c r="D9" s="43">
+      <c r="E9" s="43">
         <v>9.0972222222222218E-2</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="F9" s="43" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" s="39">
         <v>9</v>
       </c>
       <c r="B10" s="42">
         <v>46322</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" s="43">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="D10" s="43">
+      <c r="E10" s="43">
         <v>9.8611111111111108E-2</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="F10" s="43" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11" s="39">
         <v>10</v>
       </c>
       <c r="B11" s="42">
         <v>46323</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="D11" s="43">
         <v>3.1944444444444449E-2</v>
       </c>
-      <c r="D11" s="43">
+      <c r="E11" s="43">
         <v>8.6805555555555566E-2</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="F11" s="43" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12" s="39">
         <v>11</v>
       </c>
       <c r="B12" s="42">
         <v>46324</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="D12" s="43">
         <v>2.7083333333333334E-2</v>
       </c>
-      <c r="D12" s="43">
+      <c r="E12" s="43">
         <v>7.9861111111111105E-2</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="F12" s="43" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="39"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-    </row>
-    <row r="14" spans="1:5">
+    <row r="13" spans="1:6">
+      <c r="A13" s="39">
+        <v>12</v>
+      </c>
+      <c r="B13" s="42">
+        <v>46325</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="D13" s="43">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="E13" s="43">
+        <v>6.9444444444444434E-2</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="39"/>
       <c r="B14" s="42"/>
-      <c r="C14" s="43"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="43"/>
       <c r="E14" s="43"/>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="43"/>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="39"/>
       <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
+      <c r="C15" s="42"/>
       <c r="D15" s="43"/>
       <c r="E15" s="43"/>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="43"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="39"/>
       <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="43"/>
       <c r="E16" s="43"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="43"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="39"/>
       <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="43"/>
       <c r="E17" s="43"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="43"/>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="39"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="43"/>
       <c r="E18" s="43"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="43"/>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="39"/>
       <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="43"/>
       <c r="E19" s="43"/>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="43"/>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="39"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="43"/>
       <c r="E20" s="43"/>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="43"/>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="39"/>
       <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="43"/>
       <c r="E21" s="43"/>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="43"/>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="39"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="43"/>
       <c r="E22" s="43"/>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="43"/>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="39"/>
       <c r="B23" s="42"/>
-      <c r="C23" s="43"/>
+      <c r="C23" s="42"/>
       <c r="D23" s="43"/>
       <c r="E23" s="43"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="43"/>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="39"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
+      <c r="C24" s="42"/>
       <c r="D24" s="43"/>
       <c r="E24" s="43"/>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="43"/>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="39"/>
       <c r="B25" s="42"/>
-      <c r="C25" s="43"/>
+      <c r="C25" s="42"/>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="43"/>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="39"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="43"/>
+      <c r="C26" s="42"/>
       <c r="D26" s="43"/>
       <c r="E26" s="43"/>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" s="43"/>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="39"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
+      <c r="C27" s="42"/>
       <c r="D27" s="43"/>
       <c r="E27" s="43"/>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="43"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="39"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="43"/>
+      <c r="C28" s="42"/>
       <c r="D28" s="43"/>
       <c r="E28" s="43"/>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="43"/>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="39"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
+      <c r="C29" s="42"/>
       <c r="D29" s="43"/>
       <c r="E29" s="43"/>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="43"/>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="39"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="43"/>
+      <c r="C30" s="42"/>
       <c r="D30" s="43"/>
       <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
